--- a/BFD05D.xlsx
+++ b/BFD05D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2082" uniqueCount="745">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2082" uniqueCount="744">
   <si>
     <t/>
   </si>
@@ -1171,7 +1171,7 @@
     <t>20117107</t>
   </si>
   <si>
-    <t>BANGO KECAP MNS 920G</t>
+    <t>BANGO KCAP MNS 950 G</t>
   </si>
   <si>
     <t>10022534</t>
@@ -1810,9 +1810,6 @@
     <t>ETIRA TUNA RTE PDS75</t>
   </si>
   <si>
-    <t>PT,(E-4B)</t>
-  </si>
-  <si>
     <t>20143797</t>
   </si>
   <si>
@@ -2188,7 +2185,7 @@
     <t>10010805</t>
   </si>
   <si>
-    <t>SANIA MNYK GR PCH 2L</t>
+    <t>SANIA MYK GR PCH 2 L</t>
   </si>
   <si>
     <t>34</t>
@@ -2233,7 +2230,7 @@
     <t>10008989</t>
   </si>
   <si>
-    <t>BIMOLI MYK.GRG REF2L</t>
+    <t>BIMOLI MYK REF 2 L</t>
   </si>
   <si>
     <t>20140636</t>
@@ -8245,15 +8242,15 @@
         <v>11</v>
       </c>
       <c r="F280" s="1" t="s">
-        <v>599</v>
+        <v>83</v>
       </c>
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A281" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="B281" s="1" t="s">
         <v>600</v>
-      </c>
-      <c r="B281" s="1" t="s">
-        <v>601</v>
       </c>
       <c r="C281" s="1" t="s">
         <v>3</v>
@@ -8265,15 +8262,15 @@
         <v>34</v>
       </c>
       <c r="F281" s="1" t="s">
-        <v>599</v>
+        <v>83</v>
       </c>
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A282" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="B282" s="1" t="s">
         <v>602</v>
-      </c>
-      <c r="B282" s="1" t="s">
-        <v>603</v>
       </c>
       <c r="C282" s="1" t="s">
         <v>3</v>
@@ -8285,21 +8282,21 @@
         <v>15</v>
       </c>
       <c r="F282" s="1" t="s">
-        <v>599</v>
+        <v>83</v>
       </c>
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A283" s="1" t="s">
+        <v>603</v>
+      </c>
+      <c r="B283" s="1" t="s">
         <v>604</v>
       </c>
-      <c r="B283" s="1" t="s">
+      <c r="C283" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D283" s="1" t="s">
         <v>605</v>
-      </c>
-      <c r="C283" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D283" s="1" t="s">
-        <v>606</v>
       </c>
       <c r="E283" s="1" t="s">
         <v>4</v>
@@ -8310,16 +8307,16 @@
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A284" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="B284" s="1" t="s">
         <v>607</v>
       </c>
-      <c r="B284" s="1" t="s">
-        <v>608</v>
-      </c>
       <c r="C284" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D284" s="1" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="E284" s="1" t="s">
         <v>18</v>
@@ -8330,16 +8327,16 @@
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A285" s="1" t="s">
+        <v>608</v>
+      </c>
+      <c r="B285" s="1" t="s">
         <v>609</v>
       </c>
-      <c r="B285" s="1" t="s">
-        <v>610</v>
-      </c>
       <c r="C285" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D285" s="1" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="E285" s="1" t="s">
         <v>8</v>
@@ -8350,16 +8347,16 @@
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A286" s="1" t="s">
+        <v>610</v>
+      </c>
+      <c r="B286" s="1" t="s">
         <v>611</v>
       </c>
-      <c r="B286" s="1" t="s">
-        <v>612</v>
-      </c>
       <c r="C286" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D286" s="1" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="E286" s="1" t="s">
         <v>26</v>
@@ -8370,16 +8367,16 @@
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A287" s="1" t="s">
+        <v>612</v>
+      </c>
+      <c r="B287" s="1" t="s">
         <v>613</v>
       </c>
-      <c r="B287" s="1" t="s">
-        <v>614</v>
-      </c>
       <c r="C287" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D287" s="1" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="E287" s="1" t="s">
         <v>29</v>
@@ -8390,16 +8387,16 @@
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A288" s="1" t="s">
+        <v>614</v>
+      </c>
+      <c r="B288" s="1" t="s">
         <v>615</v>
       </c>
-      <c r="B288" s="1" t="s">
-        <v>616</v>
-      </c>
       <c r="C288" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D288" s="1" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="E288" s="1" t="s">
         <v>11</v>
@@ -8410,16 +8407,16 @@
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A289" s="1" t="s">
+        <v>616</v>
+      </c>
+      <c r="B289" s="1" t="s">
         <v>617</v>
       </c>
-      <c r="B289" s="1" t="s">
-        <v>618</v>
-      </c>
       <c r="C289" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D289" s="1" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="E289" s="1" t="s">
         <v>34</v>
@@ -8430,16 +8427,16 @@
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A290" s="1" t="s">
+        <v>618</v>
+      </c>
+      <c r="B290" s="1" t="s">
         <v>619</v>
       </c>
-      <c r="B290" s="1" t="s">
-        <v>620</v>
-      </c>
       <c r="C290" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D290" s="1" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="E290" s="1" t="s">
         <v>15</v>
@@ -8450,36 +8447,36 @@
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A291" s="1" t="s">
+        <v>620</v>
+      </c>
+      <c r="B291" s="1" t="s">
         <v>621</v>
       </c>
-      <c r="B291" s="1" t="s">
+      <c r="C291" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D291" s="1" t="s">
         <v>622</v>
-      </c>
-      <c r="C291" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D291" s="1" t="s">
-        <v>623</v>
       </c>
       <c r="E291" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F291" s="1" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A292" s="1" t="s">
+        <v>624</v>
+      </c>
+      <c r="B292" s="1" t="s">
         <v>625</v>
       </c>
-      <c r="B292" s="1" t="s">
-        <v>626</v>
-      </c>
       <c r="C292" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D292" s="1" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="E292" s="1" t="s">
         <v>18</v>
@@ -8490,16 +8487,16 @@
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A293" s="1" t="s">
+        <v>626</v>
+      </c>
+      <c r="B293" s="1" t="s">
         <v>627</v>
       </c>
-      <c r="B293" s="1" t="s">
-        <v>628</v>
-      </c>
       <c r="C293" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D293" s="1" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="E293" s="1" t="s">
         <v>8</v>
@@ -8510,16 +8507,16 @@
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A294" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="B294" s="1" t="s">
         <v>629</v>
       </c>
-      <c r="B294" s="1" t="s">
-        <v>630</v>
-      </c>
       <c r="C294" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D294" s="1" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="E294" s="1" t="s">
         <v>26</v>
@@ -8530,16 +8527,16 @@
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A295" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="B295" s="1" t="s">
         <v>631</v>
       </c>
-      <c r="B295" s="1" t="s">
-        <v>632</v>
-      </c>
       <c r="C295" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D295" s="1" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="E295" s="1" t="s">
         <v>29</v>
@@ -8550,16 +8547,16 @@
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A296" s="1" t="s">
+        <v>632</v>
+      </c>
+      <c r="B296" s="1" t="s">
         <v>633</v>
       </c>
-      <c r="B296" s="1" t="s">
-        <v>634</v>
-      </c>
       <c r="C296" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D296" s="1" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="E296" s="1" t="s">
         <v>11</v>
@@ -8570,16 +8567,16 @@
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A297" s="1" t="s">
+        <v>634</v>
+      </c>
+      <c r="B297" s="1" t="s">
         <v>635</v>
       </c>
-      <c r="B297" s="1" t="s">
-        <v>636</v>
-      </c>
       <c r="C297" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D297" s="1" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="E297" s="1" t="s">
         <v>34</v>
@@ -8590,16 +8587,16 @@
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A298" s="1" t="s">
+        <v>636</v>
+      </c>
+      <c r="B298" s="1" t="s">
         <v>637</v>
       </c>
-      <c r="B298" s="1" t="s">
-        <v>638</v>
-      </c>
       <c r="C298" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D298" s="1" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="E298" s="1" t="s">
         <v>15</v>
@@ -8610,16 +8607,16 @@
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A299" s="1" t="s">
+        <v>638</v>
+      </c>
+      <c r="B299" s="1" t="s">
         <v>639</v>
       </c>
-      <c r="B299" s="1" t="s">
-        <v>640</v>
-      </c>
       <c r="C299" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D299" s="1" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="E299" s="1" t="s">
         <v>156</v>
@@ -8630,16 +8627,16 @@
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A300" s="1" t="s">
+        <v>640</v>
+      </c>
+      <c r="B300" s="1" t="s">
         <v>641</v>
       </c>
-      <c r="B300" s="1" t="s">
-        <v>642</v>
-      </c>
       <c r="C300" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D300" s="1" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="E300" s="1" t="s">
         <v>173</v>
@@ -8650,16 +8647,16 @@
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A301" s="1" t="s">
+        <v>642</v>
+      </c>
+      <c r="B301" s="1" t="s">
         <v>643</v>
       </c>
-      <c r="B301" s="1" t="s">
-        <v>644</v>
-      </c>
       <c r="C301" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D301" s="1" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="E301" s="1" t="s">
         <v>176</v>
@@ -8670,16 +8667,16 @@
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A302" s="1" t="s">
+        <v>644</v>
+      </c>
+      <c r="B302" s="1" t="s">
         <v>645</v>
       </c>
-      <c r="B302" s="1" t="s">
-        <v>646</v>
-      </c>
       <c r="C302" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D302" s="1" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="E302" s="1" t="s">
         <v>179</v>
@@ -8690,16 +8687,16 @@
     </row>
     <row r="303" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A303" s="1" t="s">
+        <v>646</v>
+      </c>
+      <c r="B303" s="1" t="s">
         <v>647</v>
       </c>
-      <c r="B303" s="1" t="s">
-        <v>648</v>
-      </c>
       <c r="C303" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D303" s="1" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="E303" s="1" t="s">
         <v>182</v>
@@ -8710,16 +8707,16 @@
     </row>
     <row r="304" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A304" s="1" t="s">
+        <v>648</v>
+      </c>
+      <c r="B304" s="1" t="s">
         <v>649</v>
       </c>
-      <c r="B304" s="1" t="s">
-        <v>650</v>
-      </c>
       <c r="C304" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D304" s="1" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="E304" s="1" t="s">
         <v>185</v>
@@ -8730,16 +8727,16 @@
     </row>
     <row r="305" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A305" s="1" t="s">
+        <v>650</v>
+      </c>
+      <c r="B305" s="1" t="s">
         <v>651</v>
       </c>
-      <c r="B305" s="1" t="s">
+      <c r="C305" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D305" s="1" t="s">
         <v>652</v>
-      </c>
-      <c r="C305" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D305" s="1" t="s">
-        <v>653</v>
       </c>
       <c r="E305" s="1" t="s">
         <v>4</v>
@@ -8750,16 +8747,16 @@
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A306" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="B306" s="1" t="s">
         <v>654</v>
       </c>
-      <c r="B306" s="1" t="s">
-        <v>655</v>
-      </c>
       <c r="C306" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D306" s="1" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="E306" s="1" t="s">
         <v>18</v>
@@ -8770,16 +8767,16 @@
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A307" s="1" t="s">
+        <v>655</v>
+      </c>
+      <c r="B307" s="1" t="s">
         <v>656</v>
       </c>
-      <c r="B307" s="1" t="s">
-        <v>657</v>
-      </c>
       <c r="C307" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D307" s="1" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="E307" s="1" t="s">
         <v>8</v>
@@ -8790,16 +8787,16 @@
     </row>
     <row r="308" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A308" s="1" t="s">
+        <v>657</v>
+      </c>
+      <c r="B308" s="1" t="s">
         <v>658</v>
       </c>
-      <c r="B308" s="1" t="s">
-        <v>659</v>
-      </c>
       <c r="C308" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D308" s="1" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="E308" s="1" t="s">
         <v>26</v>
@@ -8810,16 +8807,16 @@
     </row>
     <row r="309" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A309" s="1" t="s">
+        <v>659</v>
+      </c>
+      <c r="B309" s="1" t="s">
         <v>660</v>
       </c>
-      <c r="B309" s="1" t="s">
-        <v>661</v>
-      </c>
       <c r="C309" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D309" s="1" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="E309" s="1" t="s">
         <v>29</v>
@@ -8830,16 +8827,16 @@
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A310" s="1" t="s">
+        <v>661</v>
+      </c>
+      <c r="B310" s="1" t="s">
         <v>662</v>
       </c>
-      <c r="B310" s="1" t="s">
-        <v>663</v>
-      </c>
       <c r="C310" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D310" s="1" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="E310" s="1" t="s">
         <v>34</v>
@@ -8850,16 +8847,16 @@
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A311" s="1" t="s">
+        <v>663</v>
+      </c>
+      <c r="B311" s="1" t="s">
         <v>664</v>
       </c>
-      <c r="B311" s="1" t="s">
-        <v>665</v>
-      </c>
       <c r="C311" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D311" s="1" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="E311" s="1" t="s">
         <v>15</v>
@@ -8870,16 +8867,16 @@
     </row>
     <row r="312" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A312" s="1" t="s">
+        <v>665</v>
+      </c>
+      <c r="B312" s="1" t="s">
         <v>666</v>
       </c>
-      <c r="B312" s="1" t="s">
-        <v>667</v>
-      </c>
       <c r="C312" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D312" s="1" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="E312" s="1" t="s">
         <v>156</v>
@@ -8890,16 +8887,16 @@
     </row>
     <row r="313" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A313" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="B313" s="1" t="s">
         <v>668</v>
       </c>
-      <c r="B313" s="1" t="s">
+      <c r="C313" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D313" s="1" t="s">
         <v>669</v>
-      </c>
-      <c r="C313" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D313" s="1" t="s">
-        <v>670</v>
       </c>
       <c r="E313" s="1" t="s">
         <v>4</v>
@@ -8910,16 +8907,16 @@
     </row>
     <row r="314" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A314" s="1" t="s">
+        <v>670</v>
+      </c>
+      <c r="B314" s="1" t="s">
         <v>671</v>
       </c>
-      <c r="B314" s="1" t="s">
-        <v>672</v>
-      </c>
       <c r="C314" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D314" s="1" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="E314" s="1" t="s">
         <v>18</v>
@@ -8930,16 +8927,16 @@
     </row>
     <row r="315" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A315" s="1" t="s">
+        <v>672</v>
+      </c>
+      <c r="B315" s="1" t="s">
         <v>673</v>
       </c>
-      <c r="B315" s="1" t="s">
-        <v>674</v>
-      </c>
       <c r="C315" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D315" s="1" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="E315" s="1" t="s">
         <v>8</v>
@@ -8950,16 +8947,16 @@
     </row>
     <row r="316" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A316" s="1" t="s">
+        <v>674</v>
+      </c>
+      <c r="B316" s="1" t="s">
         <v>675</v>
       </c>
-      <c r="B316" s="1" t="s">
-        <v>676</v>
-      </c>
       <c r="C316" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D316" s="1" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="E316" s="1" t="s">
         <v>26</v>
@@ -8970,16 +8967,16 @@
     </row>
     <row r="317" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A317" s="1" t="s">
+        <v>676</v>
+      </c>
+      <c r="B317" s="1" t="s">
         <v>677</v>
       </c>
-      <c r="B317" s="1" t="s">
-        <v>678</v>
-      </c>
       <c r="C317" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D317" s="1" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="E317" s="1" t="s">
         <v>29</v>
@@ -8990,16 +8987,16 @@
     </row>
     <row r="318" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A318" s="1" t="s">
+        <v>678</v>
+      </c>
+      <c r="B318" s="1" t="s">
         <v>679</v>
       </c>
-      <c r="B318" s="1" t="s">
-        <v>680</v>
-      </c>
       <c r="C318" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D318" s="1" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="E318" s="1" t="s">
         <v>11</v>
@@ -9010,16 +9007,16 @@
     </row>
     <row r="319" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A319" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="B319" s="1" t="s">
         <v>681</v>
       </c>
-      <c r="B319" s="1" t="s">
-        <v>682</v>
-      </c>
       <c r="C319" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D319" s="1" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="E319" s="1" t="s">
         <v>34</v>
@@ -9030,16 +9027,16 @@
     </row>
     <row r="320" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A320" s="1" t="s">
+        <v>682</v>
+      </c>
+      <c r="B320" s="1" t="s">
         <v>683</v>
       </c>
-      <c r="B320" s="1" t="s">
-        <v>684</v>
-      </c>
       <c r="C320" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D320" s="1" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="E320" s="1" t="s">
         <v>15</v>
@@ -9050,16 +9047,16 @@
     </row>
     <row r="321" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A321" s="1" t="s">
+        <v>684</v>
+      </c>
+      <c r="B321" s="1" t="s">
         <v>685</v>
       </c>
-      <c r="B321" s="1" t="s">
-        <v>686</v>
-      </c>
       <c r="C321" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D321" s="1" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="E321" s="1" t="s">
         <v>156</v>
@@ -9070,16 +9067,16 @@
     </row>
     <row r="322" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A322" s="1" t="s">
+        <v>686</v>
+      </c>
+      <c r="B322" s="1" t="s">
         <v>687</v>
       </c>
-      <c r="B322" s="1" t="s">
+      <c r="C322" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D322" s="1" t="s">
         <v>688</v>
-      </c>
-      <c r="C322" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D322" s="1" t="s">
-        <v>689</v>
       </c>
       <c r="E322" s="1" t="s">
         <v>4</v>
@@ -9090,16 +9087,16 @@
     </row>
     <row r="323" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A323" s="1" t="s">
+        <v>689</v>
+      </c>
+      <c r="B323" s="1" t="s">
         <v>690</v>
       </c>
-      <c r="B323" s="1" t="s">
-        <v>691</v>
-      </c>
       <c r="C323" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D323" s="1" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="E323" s="1" t="s">
         <v>18</v>
@@ -9110,16 +9107,16 @@
     </row>
     <row r="324" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A324" s="1" t="s">
+        <v>691</v>
+      </c>
+      <c r="B324" s="1" t="s">
         <v>692</v>
       </c>
-      <c r="B324" s="1" t="s">
-        <v>693</v>
-      </c>
       <c r="C324" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D324" s="1" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="E324" s="1" t="s">
         <v>8</v>
@@ -9130,16 +9127,16 @@
     </row>
     <row r="325" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A325" s="1" t="s">
+        <v>693</v>
+      </c>
+      <c r="B325" s="1" t="s">
         <v>694</v>
       </c>
-      <c r="B325" s="1" t="s">
-        <v>695</v>
-      </c>
       <c r="C325" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D325" s="1" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="E325" s="1" t="s">
         <v>26</v>
@@ -9150,16 +9147,16 @@
     </row>
     <row r="326" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A326" s="1" t="s">
+        <v>695</v>
+      </c>
+      <c r="B326" s="1" t="s">
         <v>696</v>
       </c>
-      <c r="B326" s="1" t="s">
-        <v>697</v>
-      </c>
       <c r="C326" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D326" s="1" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="E326" s="1" t="s">
         <v>29</v>
@@ -9170,16 +9167,16 @@
     </row>
     <row r="327" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A327" s="1" t="s">
+        <v>697</v>
+      </c>
+      <c r="B327" s="1" t="s">
         <v>698</v>
       </c>
-      <c r="B327" s="1" t="s">
-        <v>699</v>
-      </c>
       <c r="C327" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D327" s="1" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="E327" s="1" t="s">
         <v>11</v>
@@ -9190,16 +9187,16 @@
     </row>
     <row r="328" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A328" s="1" t="s">
+        <v>699</v>
+      </c>
+      <c r="B328" s="1" t="s">
         <v>700</v>
       </c>
-      <c r="B328" s="1" t="s">
+      <c r="C328" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D328" s="1" t="s">
         <v>701</v>
-      </c>
-      <c r="C328" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D328" s="1" t="s">
-        <v>702</v>
       </c>
       <c r="E328" s="1" t="s">
         <v>4</v>
@@ -9210,16 +9207,16 @@
     </row>
     <row r="329" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A329" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="B329" s="1" t="s">
         <v>703</v>
       </c>
-      <c r="B329" s="1" t="s">
-        <v>704</v>
-      </c>
       <c r="C329" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D329" s="1" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E329" s="1" t="s">
         <v>18</v>
@@ -9230,16 +9227,16 @@
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A330" s="1" t="s">
+        <v>704</v>
+      </c>
+      <c r="B330" s="1" t="s">
         <v>705</v>
       </c>
-      <c r="B330" s="1" t="s">
-        <v>706</v>
-      </c>
       <c r="C330" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D330" s="1" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E330" s="1" t="s">
         <v>8</v>
@@ -9250,16 +9247,16 @@
     </row>
     <row r="331" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A331" s="1" t="s">
+        <v>706</v>
+      </c>
+      <c r="B331" s="1" t="s">
         <v>707</v>
       </c>
-      <c r="B331" s="1" t="s">
-        <v>708</v>
-      </c>
       <c r="C331" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D331" s="1" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E331" s="1" t="s">
         <v>26</v>
@@ -9270,16 +9267,16 @@
     </row>
     <row r="332" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A332" s="1" t="s">
+        <v>708</v>
+      </c>
+      <c r="B332" s="1" t="s">
         <v>709</v>
       </c>
-      <c r="B332" s="1" t="s">
-        <v>710</v>
-      </c>
       <c r="C332" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D332" s="1" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E332" s="1" t="s">
         <v>29</v>
@@ -9290,16 +9287,16 @@
     </row>
     <row r="333" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A333" s="1" t="s">
+        <v>710</v>
+      </c>
+      <c r="B333" s="1" t="s">
         <v>711</v>
       </c>
-      <c r="B333" s="1" t="s">
-        <v>712</v>
-      </c>
       <c r="C333" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D333" s="1" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E333" s="1" t="s">
         <v>11</v>
@@ -9310,16 +9307,16 @@
     </row>
     <row r="334" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A334" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B334" s="1" t="s">
         <v>713</v>
       </c>
-      <c r="B334" s="1" t="s">
+      <c r="C334" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D334" s="1" t="s">
         <v>714</v>
-      </c>
-      <c r="C334" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D334" s="1" t="s">
-        <v>715</v>
       </c>
       <c r="E334" s="1" t="s">
         <v>4</v>
@@ -9330,16 +9327,16 @@
     </row>
     <row r="335" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A335" s="1" t="s">
+        <v>715</v>
+      </c>
+      <c r="B335" s="1" t="s">
         <v>716</v>
       </c>
-      <c r="B335" s="1" t="s">
-        <v>717</v>
-      </c>
       <c r="C335" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D335" s="1" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="E335" s="1" t="s">
         <v>18</v>
@@ -9350,16 +9347,16 @@
     </row>
     <row r="336" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A336" s="1" t="s">
+        <v>717</v>
+      </c>
+      <c r="B336" s="1" t="s">
         <v>718</v>
       </c>
-      <c r="B336" s="1" t="s">
-        <v>719</v>
-      </c>
       <c r="C336" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D336" s="1" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="E336" s="1" t="s">
         <v>8</v>
@@ -9370,16 +9367,16 @@
     </row>
     <row r="337" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A337" s="1" t="s">
+        <v>719</v>
+      </c>
+      <c r="B337" s="1" t="s">
         <v>720</v>
       </c>
-      <c r="B337" s="1" t="s">
-        <v>721</v>
-      </c>
       <c r="C337" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D337" s="1" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="E337" s="1" t="s">
         <v>26</v>
@@ -9390,16 +9387,16 @@
     </row>
     <row r="338" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A338" s="1" t="s">
+        <v>721</v>
+      </c>
+      <c r="B338" s="1" t="s">
         <v>722</v>
       </c>
-      <c r="B338" s="1" t="s">
-        <v>723</v>
-      </c>
       <c r="C338" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D338" s="1" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="E338" s="1" t="s">
         <v>29</v>
@@ -9410,16 +9407,16 @@
     </row>
     <row r="339" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A339" s="1" t="s">
+        <v>723</v>
+      </c>
+      <c r="B339" s="1" t="s">
         <v>724</v>
       </c>
-      <c r="B339" s="1" t="s">
+      <c r="C339" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D339" s="1" t="s">
         <v>725</v>
-      </c>
-      <c r="C339" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D339" s="1" t="s">
-        <v>726</v>
       </c>
       <c r="E339" s="1" t="s">
         <v>4</v>
@@ -9430,16 +9427,16 @@
     </row>
     <row r="340" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A340" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="B340" s="1" t="s">
         <v>727</v>
       </c>
-      <c r="B340" s="1" t="s">
-        <v>728</v>
-      </c>
       <c r="C340" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D340" s="1" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="E340" s="1" t="s">
         <v>18</v>
@@ -9450,16 +9447,16 @@
     </row>
     <row r="341" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A341" s="1" t="s">
+        <v>728</v>
+      </c>
+      <c r="B341" s="1" t="s">
         <v>729</v>
       </c>
-      <c r="B341" s="1" t="s">
-        <v>730</v>
-      </c>
       <c r="C341" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D341" s="1" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="E341" s="1" t="s">
         <v>8</v>
@@ -9470,16 +9467,16 @@
     </row>
     <row r="342" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A342" s="1" t="s">
+        <v>730</v>
+      </c>
+      <c r="B342" s="1" t="s">
         <v>731</v>
       </c>
-      <c r="B342" s="1" t="s">
-        <v>732</v>
-      </c>
       <c r="C342" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D342" s="1" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="E342" s="1" t="s">
         <v>26</v>
@@ -9490,16 +9487,16 @@
     </row>
     <row r="343" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A343" s="1" t="s">
+        <v>732</v>
+      </c>
+      <c r="B343" s="1" t="s">
         <v>733</v>
       </c>
-      <c r="B343" s="1" t="s">
-        <v>734</v>
-      </c>
       <c r="C343" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D343" s="1" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="E343" s="1" t="s">
         <v>29</v>
@@ -9510,36 +9507,36 @@
     </row>
     <row r="344" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A344" s="1" t="s">
+        <v>734</v>
+      </c>
+      <c r="B344" s="1" t="s">
         <v>735</v>
       </c>
-      <c r="B344" s="1" t="s">
+      <c r="C344" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D344" s="1" t="s">
         <v>736</v>
-      </c>
-      <c r="C344" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D344" s="1" t="s">
-        <v>737</v>
       </c>
       <c r="E344" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F344" s="1" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
     </row>
     <row r="345" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A345" s="1" t="s">
+        <v>738</v>
+      </c>
+      <c r="B345" s="1" t="s">
         <v>739</v>
       </c>
-      <c r="B345" s="1" t="s">
-        <v>740</v>
-      </c>
       <c r="C345" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D345" s="1" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="E345" s="1" t="s">
         <v>18</v>
@@ -9550,16 +9547,16 @@
     </row>
     <row r="346" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A346" s="1" t="s">
+        <v>740</v>
+      </c>
+      <c r="B346" s="1" t="s">
         <v>741</v>
       </c>
-      <c r="B346" s="1" t="s">
-        <v>742</v>
-      </c>
       <c r="C346" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D346" s="1" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="E346" s="1" t="s">
         <v>8</v>
@@ -9570,16 +9567,16 @@
     </row>
     <row r="347" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A347" s="1" t="s">
+        <v>742</v>
+      </c>
+      <c r="B347" s="1" t="s">
         <v>743</v>
       </c>
-      <c r="B347" s="1" t="s">
-        <v>744</v>
-      </c>
       <c r="C347" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D347" s="1" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="E347" s="1" t="s">
         <v>26</v>

--- a/BFD05D.xlsx
+++ b/BFD05D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2082" uniqueCount="744">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2100" uniqueCount="750">
   <si>
     <t/>
   </si>
@@ -271,304 +271,313 @@
     <t>LARISST GRM KASAR500</t>
   </si>
   <si>
+    <t>20005008</t>
+  </si>
+  <si>
+    <t>ABC TERASI UDG 20'S</t>
+  </si>
+  <si>
+    <t>20025757</t>
+  </si>
+  <si>
+    <t>PRONAS NS GRG SP 110</t>
+  </si>
+  <si>
+    <t>20140350</t>
+  </si>
+  <si>
+    <t>LARISST BMB MASAK 90</t>
+  </si>
+  <si>
+    <t>20045204</t>
+  </si>
+  <si>
+    <t>AJINOMOTO RP 5000,-</t>
+  </si>
+  <si>
+    <t>20123853</t>
+  </si>
+  <si>
+    <t>SASA 5.000 80G</t>
+  </si>
+  <si>
+    <t>10003696</t>
+  </si>
+  <si>
+    <t>SASA BUMBU MSK 250GR</t>
+  </si>
+  <si>
+    <t>10003697</t>
+  </si>
+  <si>
+    <t>AJINOMOTO BB.MSK 250</t>
+  </si>
+  <si>
+    <t>20134507</t>
+  </si>
+  <si>
+    <t>TUDUNG BMB NS UDUK27</t>
+  </si>
+  <si>
+    <t>20134777</t>
+  </si>
+  <si>
+    <t>SASA KARI JPG ORI 40</t>
+  </si>
+  <si>
+    <t>20136577</t>
+  </si>
+  <si>
+    <t>TUDUNG BMB PRLDK 50G</t>
+  </si>
+  <si>
+    <t>20136743</t>
+  </si>
+  <si>
+    <t>TDUNG BMB NP.RDNG 27</t>
+  </si>
+  <si>
+    <t>20134778</t>
+  </si>
+  <si>
+    <t>SASA KARI JPG PDS 40</t>
+  </si>
+  <si>
+    <t>20137258</t>
+  </si>
+  <si>
+    <t>RASA/M GULAI AYAM40G</t>
+  </si>
+  <si>
+    <t>20138072</t>
+  </si>
+  <si>
+    <t>RASA/M OPOR AYAM 40G</t>
+  </si>
+  <si>
+    <t>20138843</t>
+  </si>
+  <si>
+    <t>R/MASA SYR LODEH 25G</t>
+  </si>
+  <si>
+    <t>20025563</t>
+  </si>
+  <si>
+    <t>SASA BMB LUMUR AYM26</t>
+  </si>
+  <si>
+    <t>20057290</t>
+  </si>
+  <si>
+    <t>SASA BU AYAM KNG 25G</t>
+  </si>
+  <si>
+    <t>20059859</t>
+  </si>
+  <si>
+    <t>KOBE BMB N/GRG PDS20</t>
+  </si>
+  <si>
+    <t>20136397</t>
+  </si>
+  <si>
+    <t>KB BMB AYM LNGKS 80G</t>
+  </si>
+  <si>
+    <t>10007775</t>
+  </si>
+  <si>
+    <t>A/SAJIKU NASI G.AY20</t>
+  </si>
+  <si>
+    <t>10013821</t>
+  </si>
+  <si>
+    <t>A/SAJIKU NASI G.PD20</t>
+  </si>
+  <si>
+    <t>10013823</t>
+  </si>
+  <si>
+    <t>A/SAJIKU BB.AYM GR24</t>
+  </si>
+  <si>
+    <t>20103449</t>
+  </si>
+  <si>
+    <t>SAJIKU NSI GRG SPL20</t>
+  </si>
+  <si>
+    <t>10035898</t>
+  </si>
+  <si>
+    <t>A/MASAKO AYAM 94GR</t>
+  </si>
+  <si>
+    <t>20038548</t>
+  </si>
+  <si>
+    <t>MASAKO SAPI 230GR</t>
+  </si>
+  <si>
+    <t>20038549</t>
+  </si>
+  <si>
+    <t>A/MASAKO AYAM 230GR</t>
+  </si>
+  <si>
+    <t>20143858</t>
+  </si>
+  <si>
+    <t>AJNMTO SJKU RNDNG60</t>
+  </si>
+  <si>
+    <t>10035899</t>
+  </si>
+  <si>
+    <t>A/MASAKO SAPI 94GR</t>
+  </si>
+  <si>
+    <t>20135316</t>
+  </si>
+  <si>
+    <t>LARISST BMB JMR 40G</t>
+  </si>
+  <si>
+    <t>20143857</t>
+  </si>
+  <si>
+    <t>AJNMTO SJIKU GULAI50</t>
+  </si>
+  <si>
+    <t>20134250</t>
+  </si>
+  <si>
+    <t>AJ/MASAKO JAMUR 40G</t>
+  </si>
+  <si>
+    <t>20143860</t>
+  </si>
+  <si>
+    <t>KPOE B/R KLDU JMR 80</t>
+  </si>
+  <si>
+    <t>20098663</t>
+  </si>
+  <si>
+    <t>TOTOLE KLD JMUR 40G</t>
+  </si>
+  <si>
+    <t>20104719</t>
+  </si>
+  <si>
+    <t>TOTOLE KLD JMUR 80G</t>
+  </si>
+  <si>
+    <t>10006884</t>
+  </si>
+  <si>
+    <t>ABC MINYAK WIJEN.195</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>20031771</t>
+  </si>
+  <si>
+    <t>LKK PURE SSME OIL115</t>
+  </si>
+  <si>
+    <t>20085784</t>
+  </si>
+  <si>
+    <t>LKK OYSTER SAUCE 145</t>
+  </si>
+  <si>
+    <t>10036703</t>
+  </si>
+  <si>
+    <t>INDOFOOD KCP ASIN140</t>
+  </si>
+  <si>
+    <t>10000324</t>
+  </si>
+  <si>
+    <t>ABC KECAP ASIN 131ML</t>
+  </si>
+  <si>
+    <t>20009966</t>
+  </si>
+  <si>
+    <t>SAORI SAUS TIRAM 133</t>
+  </si>
+  <si>
+    <t>20009973</t>
+  </si>
+  <si>
+    <t>SAORI SAUS TERIYK135</t>
+  </si>
+  <si>
+    <t>20103453</t>
+  </si>
+  <si>
+    <t>SAORI SAUS LD HTM133</t>
+  </si>
+  <si>
+    <t>20142668</t>
+  </si>
+  <si>
+    <t>SAORI SS YAKINIKU133</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>20044599</t>
+  </si>
+  <si>
+    <t>SAORI SAUS TIRAM 270</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>20038236</t>
+  </si>
+  <si>
+    <t>ABC SAUS TIRAM 135</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>20071507</t>
+  </si>
+  <si>
+    <t>MAGGI SAUS TIRAM 150</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>20117166</t>
+  </si>
+  <si>
+    <t>MAESTRO SS TIRAM 270</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
     <t>20036713</t>
   </si>
   <si>
     <t>IDM CUKA BTL150ML</t>
   </si>
   <si>
-    <t>20005008</t>
-  </si>
-  <si>
-    <t>ABC TERASI UDG 20'S</t>
-  </si>
-  <si>
-    <t>20025757</t>
-  </si>
-  <si>
-    <t>PRONAS NS GRG SP 110</t>
-  </si>
-  <si>
-    <t>20140350</t>
-  </si>
-  <si>
-    <t>LARISST BMB MASAK 90</t>
-  </si>
-  <si>
-    <t>20045204</t>
-  </si>
-  <si>
-    <t>AJINOMOTO RP 5000,-</t>
-  </si>
-  <si>
-    <t>20123853</t>
-  </si>
-  <si>
-    <t>SASA 5.000 80G</t>
-  </si>
-  <si>
-    <t>10003696</t>
-  </si>
-  <si>
-    <t>SASA BUMBU MSK 250GR</t>
-  </si>
-  <si>
-    <t>10003697</t>
-  </si>
-  <si>
-    <t>AJINOMOTO BB.MSK 250</t>
-  </si>
-  <si>
-    <t>20134507</t>
-  </si>
-  <si>
-    <t>TUDUNG BMB NS UDUK27</t>
-  </si>
-  <si>
-    <t>20134777</t>
-  </si>
-  <si>
-    <t>SASA KARI JPG ORI 40</t>
-  </si>
-  <si>
-    <t>20136577</t>
-  </si>
-  <si>
-    <t>TUDUNG BMB PRLDK 50G</t>
-  </si>
-  <si>
-    <t>20136743</t>
-  </si>
-  <si>
-    <t>TDUNG BMB NP.RDNG 27</t>
-  </si>
-  <si>
-    <t>20134778</t>
-  </si>
-  <si>
-    <t>SASA KARI JPG PDS 40</t>
-  </si>
-  <si>
-    <t>20137258</t>
-  </si>
-  <si>
-    <t>RASA/M GULAI AYAM40G</t>
-  </si>
-  <si>
-    <t>20138072</t>
-  </si>
-  <si>
-    <t>RASA/M OPOR AYAM 40G</t>
-  </si>
-  <si>
-    <t>20138843</t>
-  </si>
-  <si>
-    <t>R/MASA SYR LODEH 25G</t>
-  </si>
-  <si>
-    <t>20025563</t>
-  </si>
-  <si>
-    <t>SASA BMB LUMUR AYM26</t>
-  </si>
-  <si>
-    <t>20057290</t>
-  </si>
-  <si>
-    <t>SASA BU AYAM KNG 25G</t>
-  </si>
-  <si>
-    <t>20059859</t>
-  </si>
-  <si>
-    <t>KOBE BMB N/GRG PDS20</t>
-  </si>
-  <si>
-    <t>20136397</t>
-  </si>
-  <si>
-    <t>KB BMB AYM LNGKS 80G</t>
-  </si>
-  <si>
-    <t>10007775</t>
-  </si>
-  <si>
-    <t>A/SAJIKU NASI G.AY20</t>
-  </si>
-  <si>
-    <t>10013821</t>
-  </si>
-  <si>
-    <t>A/SAJIKU NASI G.PD20</t>
-  </si>
-  <si>
-    <t>10013823</t>
-  </si>
-  <si>
-    <t>A/SAJIKU BB.AYM GR24</t>
-  </si>
-  <si>
-    <t>20103449</t>
-  </si>
-  <si>
-    <t>SAJIKU NSI GRG SPL20</t>
-  </si>
-  <si>
-    <t>10035898</t>
-  </si>
-  <si>
-    <t>A/MASAKO AYAM 94GR</t>
-  </si>
-  <si>
-    <t>20038548</t>
-  </si>
-  <si>
-    <t>MASAKO SAPI 230GR</t>
-  </si>
-  <si>
-    <t>20038549</t>
-  </si>
-  <si>
-    <t>A/MASAKO AYAM 230GR</t>
-  </si>
-  <si>
-    <t>20143858</t>
-  </si>
-  <si>
-    <t>AJNMTO SJKU RNDNG60</t>
-  </si>
-  <si>
-    <t>10035899</t>
-  </si>
-  <si>
-    <t>A/MASAKO SAPI 94GR</t>
-  </si>
-  <si>
-    <t>20135316</t>
-  </si>
-  <si>
-    <t>LARISST BMB JMR 40G</t>
-  </si>
-  <si>
-    <t>20143857</t>
-  </si>
-  <si>
-    <t>AJNMTO SJIKU GULAI50</t>
-  </si>
-  <si>
-    <t>20104719</t>
-  </si>
-  <si>
-    <t>TOTOLE KLD JMUR 80G</t>
-  </si>
-  <si>
-    <t>20143860</t>
-  </si>
-  <si>
-    <t>KPOE B/R KLDU JMR 80</t>
-  </si>
-  <si>
-    <t>20098663</t>
-  </si>
-  <si>
-    <t>TOTOLE KLD JMUR 40G</t>
-  </si>
-  <si>
-    <t>10006884</t>
-  </si>
-  <si>
-    <t>ABC MINYAK WIJEN.195</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>20031771</t>
-  </si>
-  <si>
-    <t>LKK PURE SSME OIL115</t>
-  </si>
-  <si>
-    <t>20085784</t>
-  </si>
-  <si>
-    <t>LKK OYSTER SAUCE 145</t>
-  </si>
-  <si>
-    <t>10036703</t>
-  </si>
-  <si>
-    <t>INDOFOOD KCP ASIN140</t>
-  </si>
-  <si>
-    <t>10000324</t>
-  </si>
-  <si>
-    <t>ABC KECAP ASIN 131ML</t>
-  </si>
-  <si>
-    <t>20009966</t>
-  </si>
-  <si>
-    <t>SAORI SAUS TIRAM 133</t>
-  </si>
-  <si>
-    <t>20009973</t>
-  </si>
-  <si>
-    <t>SAORI SAUS TERIYK135</t>
-  </si>
-  <si>
-    <t>20103453</t>
-  </si>
-  <si>
-    <t>SAORI SAUS LD HTM133</t>
-  </si>
-  <si>
-    <t>20142668</t>
-  </si>
-  <si>
-    <t>SAORI SS YAKINIKU133</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>20044599</t>
-  </si>
-  <si>
-    <t>SAORI SAUS TIRAM 270</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>20038236</t>
-  </si>
-  <si>
-    <t>ABC SAUS TIRAM 135</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>20071507</t>
-  </si>
-  <si>
-    <t>MAGGI SAUS TIRAM 150</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>20117166</t>
-  </si>
-  <si>
-    <t>MAESTRO SS TIRAM 270</t>
-  </si>
-  <si>
-    <t>14</t>
+    <t>15</t>
   </si>
   <si>
     <t>20015850</t>
@@ -721,9 +730,6 @@
     <t>2 BELIBIS SAUS 235ML</t>
   </si>
   <si>
-    <t>15</t>
-  </si>
-  <si>
     <t>20082351</t>
   </si>
   <si>
@@ -982,22 +988,46 @@
     <t>INDOFOOD SEMUR 50G</t>
   </si>
   <si>
+    <t>20143835</t>
+  </si>
+  <si>
+    <t>INDFD RACIK TOMYUM60</t>
+  </si>
+  <si>
+    <t>20013616</t>
+  </si>
+  <si>
+    <t>INDOFD RACIK N.GRG20</t>
+  </si>
+  <si>
+    <t>20013617</t>
+  </si>
+  <si>
+    <t>INDOFD RACIK S.ASM33</t>
+  </si>
+  <si>
+    <t>20133255</t>
+  </si>
+  <si>
+    <t>INDOFOOD AYM MNTGA50</t>
+  </si>
+  <si>
     <t>20139390</t>
   </si>
   <si>
     <t>INDO RACIK BALADO 55</t>
   </si>
   <si>
-    <t>20013616</t>
-  </si>
-  <si>
-    <t>INDOFD RACIK N.GRG20</t>
-  </si>
-  <si>
-    <t>20013617</t>
-  </si>
-  <si>
-    <t>INDOFD RACIK S.ASM33</t>
+    <t>20014281</t>
+  </si>
+  <si>
+    <t>INDOF RACIK AYM.GR26</t>
+  </si>
+  <si>
+    <t>20023890</t>
+  </si>
+  <si>
+    <t>INDOFD RACIK S.SOP20</t>
   </si>
   <si>
     <t>20036783</t>
@@ -1006,10 +1036,22 @@
     <t>INDOFD RCK IKN GRG20</t>
   </si>
   <si>
-    <t>20133255</t>
-  </si>
-  <si>
-    <t>INDOFOOD AYM MNTGA50</t>
+    <t>20113574</t>
+  </si>
+  <si>
+    <t>INDF RCK NSGOR SS 3S</t>
+  </si>
+  <si>
+    <t>10040150</t>
+  </si>
+  <si>
+    <t>INDOF/TBR BK BBQ 25G</t>
+  </si>
+  <si>
+    <t>10040157</t>
+  </si>
+  <si>
+    <t>INDOF TBR BK KEJU25G</t>
   </si>
   <si>
     <t>20013341</t>
@@ -1018,34 +1060,16 @@
     <t>BAMBOE RENDANG 35G</t>
   </si>
   <si>
-    <t>20014281</t>
-  </si>
-  <si>
-    <t>INDOF RACIK AYM.GR26</t>
-  </si>
-  <si>
-    <t>20023890</t>
-  </si>
-  <si>
-    <t>INDOFD RACIK S.SOP20</t>
-  </si>
-  <si>
-    <t>20113574</t>
-  </si>
-  <si>
-    <t>INDF RCK NSGOR SS 3S</t>
-  </si>
-  <si>
-    <t>10040150</t>
-  </si>
-  <si>
-    <t>INDOF/TBR BK BBQ 25G</t>
-  </si>
-  <si>
-    <t>10040157</t>
-  </si>
-  <si>
-    <t>INDOF TBR BK KEJU25G</t>
+    <t>20140677</t>
+  </si>
+  <si>
+    <t>IND TABURI GAS PD 25</t>
+  </si>
+  <si>
+    <t>20013333</t>
+  </si>
+  <si>
+    <t>BAMBOE BUMBU RAWON54</t>
   </si>
   <si>
     <t>20013345</t>
@@ -1054,18 +1078,6 @@
     <t>BAMBOE NASI GRG 40G</t>
   </si>
   <si>
-    <t>20140677</t>
-  </si>
-  <si>
-    <t>IND TABURI GAS PD 25</t>
-  </si>
-  <si>
-    <t>20013333</t>
-  </si>
-  <si>
-    <t>BAMBOE BUMBU RAWON54</t>
-  </si>
-  <si>
     <t>20021359</t>
   </si>
   <si>
@@ -1078,12 +1090,30 @@
     <t>BAMBOE BMB TOM YUM60</t>
   </si>
   <si>
+    <t>20139784</t>
+  </si>
+  <si>
+    <t>ROYCO SOTO AYAM 40G</t>
+  </si>
+  <si>
     <t>20139801</t>
   </si>
   <si>
     <t>ROYCO RENDANG 45G</t>
   </si>
   <si>
+    <t>20139802</t>
+  </si>
+  <si>
+    <t>ROYCO OPOR AYAM 45G</t>
+  </si>
+  <si>
+    <t>20142448</t>
+  </si>
+  <si>
+    <t>ROYCO KALDU AYAM 210</t>
+  </si>
+  <si>
     <t>10005820</t>
   </si>
   <si>
@@ -1093,24 +1123,6 @@
     <t>RT,(E-0.5B)</t>
   </si>
   <si>
-    <t>20139784</t>
-  </si>
-  <si>
-    <t>ROYCO SOTO AYAM 40G</t>
-  </si>
-  <si>
-    <t>20139802</t>
-  </si>
-  <si>
-    <t>ROYCO OPOR AYAM 45G</t>
-  </si>
-  <si>
-    <t>20142448</t>
-  </si>
-  <si>
-    <t>ROYCO KALDU AYAM 210</t>
-  </si>
-  <si>
     <t>20142447</t>
   </si>
   <si>
@@ -1165,7 +1177,7 @@
     <t>10008819</t>
   </si>
   <si>
-    <t>BANGO KECAP MNS 685G</t>
+    <t>BANGO KCAP MNS 700 G</t>
   </si>
   <si>
     <t>20117107</t>
@@ -1342,15 +1354,21 @@
     <t>MMSUKA PNCAKE MIX190</t>
   </si>
   <si>
+    <t>20134989</t>
+  </si>
+  <si>
+    <t>MAHORHR GL ARN 200ML</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
     <t>20071479</t>
   </si>
   <si>
     <t>L'AGIE CHOCO CHIP 45</t>
   </si>
   <si>
-    <t>20</t>
-  </si>
-  <si>
     <t>10000501</t>
   </si>
   <si>
@@ -2152,7 +2170,7 @@
     <t>20037566</t>
   </si>
   <si>
-    <t>SOVIA MNYK GR PCH 2L</t>
+    <t>SOVIA MYK GR PCH 2 L</t>
   </si>
   <si>
     <t>33</t>
@@ -2167,7 +2185,7 @@
     <t>20140913</t>
   </si>
   <si>
-    <t>SOVIA MNYK GR PCH1.8</t>
+    <t>SOVIA MYK GR 1.8 L</t>
   </si>
   <si>
     <t>20077116</t>
@@ -2194,7 +2212,7 @@
     <t>10005838</t>
   </si>
   <si>
-    <t>FILMA MINYAK GR RF2L</t>
+    <t>FILMA MYK GR RF 2 L</t>
   </si>
   <si>
     <t>20016512</t>
@@ -2242,7 +2260,7 @@
     <t>10003974</t>
   </si>
   <si>
-    <t>TROPICAL MNYK BTL 2L</t>
+    <t>TROPICAL MYK BTL 2 L</t>
   </si>
 </sst>
 </file>
@@ -2635,7 +2653,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F347"/>
+  <dimension ref="A1:F350"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -3376,10 +3394,10 @@
         <v>3</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>5</v>
@@ -3399,10 +3417,10 @@
         <v>34</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -3419,10 +3437,10 @@
         <v>34</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -3439,10 +3457,10 @@
         <v>34</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>41</v>
+        <v>12</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -3459,10 +3477,10 @@
         <v>34</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -3479,10 +3497,10 @@
         <v>34</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>23</v>
+        <v>83</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -3499,10 +3517,10 @@
         <v>34</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>83</v>
+        <v>12</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -3516,10 +3534,10 @@
         <v>3</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>12</v>
@@ -3542,7 +3560,7 @@
         <v>4</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -3562,7 +3580,7 @@
         <v>4</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -3599,10 +3617,10 @@
         <v>15</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -3622,7 +3640,7 @@
         <v>18</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -3662,7 +3680,7 @@
         <v>18</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -3679,10 +3697,10 @@
         <v>15</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
@@ -3722,7 +3740,7 @@
         <v>8</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -3742,7 +3760,7 @@
         <v>8</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -3759,7 +3777,7 @@
         <v>15</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>12</v>
@@ -3839,7 +3857,7 @@
         <v>15</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>12</v>
@@ -3919,7 +3937,7 @@
         <v>15</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>12</v>
@@ -3942,7 +3960,7 @@
         <v>11</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>12</v>
+        <v>41</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
@@ -3962,7 +3980,7 @@
         <v>11</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>41</v>
+        <v>12</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
@@ -3979,7 +3997,7 @@
         <v>15</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>12</v>
@@ -4002,7 +4020,7 @@
         <v>34</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
@@ -4019,10 +4037,10 @@
         <v>15</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>80</v>
+        <v>5</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
@@ -4316,21 +4334,21 @@
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>4</v>
+        <v>188</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>3</v>
@@ -4339,7 +4357,7 @@
         <v>173</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>23</v>
@@ -4347,10 +4365,10 @@
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>3</v>
@@ -4359,7 +4377,7 @@
         <v>173</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>23</v>
@@ -4367,10 +4385,10 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>3</v>
@@ -4379,7 +4397,7 @@
         <v>173</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>23</v>
@@ -4387,10 +4405,10 @@
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>3</v>
@@ -4399,18 +4417,18 @@
         <v>173</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>3</v>
@@ -4419,7 +4437,7 @@
         <v>173</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>5</v>
@@ -4427,10 +4445,10 @@
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>3</v>
@@ -4439,7 +4457,7 @@
         <v>173</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>5</v>
@@ -4447,10 +4465,10 @@
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>3</v>
@@ -4459,7 +4477,7 @@
         <v>173</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>5</v>
@@ -4467,10 +4485,10 @@
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>3</v>
@@ -4479,18 +4497,18 @@
         <v>173</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>156</v>
+        <v>15</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>3</v>
@@ -4499,7 +4517,7 @@
         <v>173</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>23</v>
@@ -4507,10 +4525,10 @@
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>3</v>
@@ -4519,27 +4537,27 @@
         <v>173</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="E95" s="1" t="s">
         <v>176</v>
-      </c>
-      <c r="E95" s="1" t="s">
-        <v>18</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>5</v>
@@ -4547,10 +4565,10 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>3</v>
@@ -4559,7 +4577,7 @@
         <v>176</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>5</v>
@@ -4567,10 +4585,10 @@
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>3</v>
@@ -4579,7 +4597,7 @@
         <v>176</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>5</v>
@@ -4587,10 +4605,10 @@
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>3</v>
@@ -4599,7 +4617,7 @@
         <v>176</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>5</v>
@@ -4607,10 +4625,10 @@
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>3</v>
@@ -4619,18 +4637,18 @@
         <v>176</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>3</v>
@@ -4639,7 +4657,7 @@
         <v>176</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>23</v>
@@ -4647,10 +4665,10 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>3</v>
@@ -4659,7 +4677,7 @@
         <v>176</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>23</v>
@@ -4667,10 +4685,10 @@
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>3</v>
@@ -4679,7 +4697,7 @@
         <v>176</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>156</v>
+        <v>15</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>23</v>
@@ -4687,10 +4705,10 @@
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>3</v>
@@ -4699,7 +4717,7 @@
         <v>176</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>23</v>
@@ -4707,10 +4725,10 @@
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>3</v>
@@ -4719,18 +4737,18 @@
         <v>176</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>3</v>
@@ -4739,7 +4757,7 @@
         <v>176</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>12</v>
@@ -4747,10 +4765,10 @@
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>3</v>
@@ -4759,18 +4777,18 @@
         <v>176</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>3</v>
@@ -4779,7 +4797,7 @@
         <v>176</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>5</v>
@@ -4787,10 +4805,10 @@
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>3</v>
@@ -4799,7 +4817,7 @@
         <v>176</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>236</v>
+        <v>185</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>5</v>
@@ -4819,18 +4837,18 @@
         <v>176</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>239</v>
+        <v>188</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="B110" s="1" t="s">
         <v>240</v>
-      </c>
-      <c r="B110" s="1" t="s">
-        <v>241</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>3</v>
@@ -4839,7 +4857,7 @@
         <v>176</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>23</v>
@@ -4847,22 +4865,22 @@
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="B111" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="B111" s="1" t="s">
+      <c r="C111" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D111" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="E111" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="C111" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D111" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="E111" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F111" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
@@ -4879,7 +4897,7 @@
         <v>179</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>5</v>
@@ -4899,10 +4917,10 @@
         <v>179</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
@@ -4919,7 +4937,7 @@
         <v>179</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>23</v>
@@ -4939,7 +4957,7 @@
         <v>179</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>23</v>
@@ -4959,7 +4977,7 @@
         <v>179</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>23</v>
@@ -4979,7 +4997,7 @@
         <v>179</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>23</v>
@@ -4999,10 +5017,10 @@
         <v>179</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
@@ -5019,10 +5037,10 @@
         <v>179</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>156</v>
+        <v>15</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
@@ -5036,13 +5054,13 @@
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>4</v>
+        <v>156</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
@@ -5059,10 +5077,10 @@
         <v>182</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
@@ -5079,7 +5097,7 @@
         <v>182</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>12</v>
@@ -5099,10 +5117,10 @@
         <v>182</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
@@ -5119,10 +5137,10 @@
         <v>182</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
@@ -5139,7 +5157,7 @@
         <v>182</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>12</v>
@@ -5159,7 +5177,7 @@
         <v>182</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>12</v>
@@ -5179,7 +5197,7 @@
         <v>182</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>12</v>
@@ -5199,7 +5217,7 @@
         <v>182</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>156</v>
+        <v>15</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>12</v>
@@ -5219,7 +5237,7 @@
         <v>182</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>12</v>
@@ -5236,10 +5254,10 @@
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>4</v>
+        <v>173</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>12</v>
@@ -5259,7 +5277,7 @@
         <v>185</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>12</v>
@@ -5279,7 +5297,7 @@
         <v>185</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>12</v>
@@ -5299,10 +5317,10 @@
         <v>185</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
@@ -5319,10 +5337,10 @@
         <v>185</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
@@ -5339,7 +5357,7 @@
         <v>185</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>12</v>
@@ -5359,7 +5377,7 @@
         <v>185</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>12</v>
@@ -5379,10 +5397,10 @@
         <v>185</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
@@ -5399,7 +5417,7 @@
         <v>185</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>156</v>
+        <v>15</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>23</v>
@@ -5419,10 +5437,10 @@
         <v>185</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>176</v>
+        <v>156</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
@@ -5439,7 +5457,7 @@
         <v>185</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="F140" s="1" t="s">
         <v>41</v>
@@ -5459,7 +5477,7 @@
         <v>185</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="F141" s="1" t="s">
         <v>41</v>
@@ -5479,7 +5497,7 @@
         <v>185</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="F142" s="1" t="s">
         <v>41</v>
@@ -5499,7 +5517,7 @@
         <v>185</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>236</v>
+        <v>185</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>41</v>
@@ -5516,13 +5534,13 @@
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>236</v>
+        <v>185</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>4</v>
+        <v>188</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
@@ -5536,7 +5554,7 @@
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>236</v>
+        <v>188</v>
       </c>
       <c r="E145" s="1" t="s">
         <v>4</v>
@@ -5556,7 +5574,7 @@
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>236</v>
+        <v>188</v>
       </c>
       <c r="E146" s="1" t="s">
         <v>4</v>
@@ -5576,7 +5594,7 @@
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>236</v>
+        <v>188</v>
       </c>
       <c r="E147" s="1" t="s">
         <v>4</v>
@@ -5596,10 +5614,10 @@
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>236</v>
+        <v>188</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>23</v>
@@ -5616,7 +5634,7 @@
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>236</v>
+        <v>188</v>
       </c>
       <c r="E149" s="1" t="s">
         <v>18</v>
@@ -5636,7 +5654,7 @@
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>236</v>
+        <v>188</v>
       </c>
       <c r="E150" s="1" t="s">
         <v>18</v>
@@ -5656,7 +5674,7 @@
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>236</v>
+        <v>188</v>
       </c>
       <c r="E151" s="1" t="s">
         <v>18</v>
@@ -5676,13 +5694,13 @@
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>236</v>
+        <v>188</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
@@ -5696,7 +5714,7 @@
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>236</v>
+        <v>188</v>
       </c>
       <c r="E153" s="1" t="s">
         <v>8</v>
@@ -5716,7 +5734,7 @@
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>236</v>
+        <v>188</v>
       </c>
       <c r="E154" s="1" t="s">
         <v>8</v>
@@ -5736,7 +5754,7 @@
         <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>236</v>
+        <v>188</v>
       </c>
       <c r="E155" s="1" t="s">
         <v>8</v>
@@ -5756,10 +5774,10 @@
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>236</v>
+        <v>188</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>23</v>
@@ -5776,7 +5794,7 @@
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>236</v>
+        <v>188</v>
       </c>
       <c r="E157" s="1" t="s">
         <v>26</v>
@@ -5796,7 +5814,7 @@
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>236</v>
+        <v>188</v>
       </c>
       <c r="E158" s="1" t="s">
         <v>26</v>
@@ -5816,13 +5834,13 @@
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>236</v>
+        <v>188</v>
       </c>
       <c r="E159" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
@@ -5836,13 +5854,13 @@
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>236</v>
+        <v>188</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
@@ -5856,7 +5874,7 @@
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>236</v>
+        <v>188</v>
       </c>
       <c r="E161" s="1" t="s">
         <v>29</v>
@@ -5876,7 +5894,7 @@
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>236</v>
+        <v>188</v>
       </c>
       <c r="E162" s="1" t="s">
         <v>29</v>
@@ -5896,7 +5914,7 @@
         <v>3</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>236</v>
+        <v>188</v>
       </c>
       <c r="E163" s="1" t="s">
         <v>29</v>
@@ -5916,10 +5934,10 @@
         <v>3</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>236</v>
+        <v>188</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F164" s="1" t="s">
         <v>23</v>
@@ -5936,7 +5954,7 @@
         <v>3</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>236</v>
+        <v>188</v>
       </c>
       <c r="E165" s="1" t="s">
         <v>11</v>
@@ -5956,7 +5974,7 @@
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>236</v>
+        <v>188</v>
       </c>
       <c r="E166" s="1" t="s">
         <v>11</v>
@@ -5976,13 +5994,13 @@
         <v>3</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>236</v>
+        <v>188</v>
       </c>
       <c r="E167" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
@@ -5996,27 +6014,27 @@
         <v>3</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>236</v>
+        <v>188</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>359</v>
+        <v>23</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="B169" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="B169" s="1" t="s">
-        <v>361</v>
-      </c>
       <c r="C169" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>236</v>
+        <v>188</v>
       </c>
       <c r="E169" s="1" t="s">
         <v>34</v>
@@ -6027,16 +6045,16 @@
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="B170" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="B170" s="1" t="s">
-        <v>363</v>
-      </c>
       <c r="C170" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>236</v>
+        <v>188</v>
       </c>
       <c r="E170" s="1" t="s">
         <v>34</v>
@@ -6047,16 +6065,16 @@
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="B171" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="B171" s="1" t="s">
-        <v>365</v>
-      </c>
       <c r="C171" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>236</v>
+        <v>188</v>
       </c>
       <c r="E171" s="1" t="s">
         <v>34</v>
@@ -6067,19 +6085,19 @@
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="B172" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="B172" s="1" t="s">
-        <v>367</v>
-      </c>
       <c r="C172" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>236</v>
+        <v>188</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F172" s="1" t="s">
         <v>12</v>
@@ -6087,22 +6105,22 @@
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="B173" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="B173" s="1" t="s">
+      <c r="C173" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D173" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="E173" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F173" s="1" t="s">
         <v>369</v>
-      </c>
-      <c r="C173" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D173" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="E173" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F173" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
@@ -6116,10 +6134,10 @@
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>239</v>
+        <v>188</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F174" s="1" t="s">
         <v>12</v>
@@ -6136,13 +6154,13 @@
         <v>3</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
@@ -6156,53 +6174,53 @@
         <v>3</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>376</v>
+        <v>12</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="B177" s="1" t="s">
         <v>377</v>
       </c>
-      <c r="B177" s="1" t="s">
-        <v>378</v>
-      </c>
       <c r="C177" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>83</v>
+        <v>5</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="B178" s="1" t="s">
         <v>379</v>
       </c>
-      <c r="B178" s="1" t="s">
+      <c r="C178" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D178" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="E178" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F178" s="1" t="s">
         <v>380</v>
-      </c>
-      <c r="C178" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D178" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="E178" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F178" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
@@ -6216,13 +6234,13 @@
         <v>3</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>23</v>
+        <v>83</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
@@ -6236,13 +6254,13 @@
         <v>3</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>359</v>
+        <v>12</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
@@ -6256,13 +6274,13 @@
         <v>3</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>359</v>
+        <v>23</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
@@ -6276,13 +6294,13 @@
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F182" s="1" t="s">
-        <v>5</v>
+        <v>369</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
@@ -6296,13 +6314,13 @@
         <v>3</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>5</v>
+        <v>369</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
@@ -6316,10 +6334,10 @@
         <v>3</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="F184" s="1" t="s">
         <v>5</v>
@@ -6336,13 +6354,13 @@
         <v>3</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
@@ -6356,13 +6374,13 @@
         <v>3</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
@@ -6376,10 +6394,10 @@
         <v>3</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F187" s="1" t="s">
         <v>12</v>
@@ -6396,10 +6414,10 @@
         <v>3</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>401</v>
+        <v>244</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="F188" s="1" t="s">
         <v>12</v>
@@ -6407,19 +6425,19 @@
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="B189" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="B189" s="1" t="s">
-        <v>403</v>
-      </c>
       <c r="C189" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>401</v>
+        <v>244</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F189" s="1" t="s">
         <v>12</v>
@@ -6427,22 +6445,22 @@
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="B190" s="1" t="s">
         <v>404</v>
       </c>
-      <c r="B190" s="1" t="s">
+      <c r="C190" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D190" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="C190" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D190" s="1" t="s">
-        <v>401</v>
-      </c>
       <c r="E190" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F190" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
@@ -6456,13 +6474,13 @@
         <v>3</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F191" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
@@ -6476,13 +6494,13 @@
         <v>3</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="F192" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
@@ -6496,10 +6514,10 @@
         <v>3</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F193" s="1" t="s">
         <v>23</v>
@@ -6516,13 +6534,13 @@
         <v>3</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F194" s="1" t="s">
-        <v>359</v>
+        <v>12</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
@@ -6536,13 +6554,13 @@
         <v>3</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F195" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
@@ -6556,13 +6574,13 @@
         <v>3</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>156</v>
+        <v>34</v>
       </c>
       <c r="F196" s="1" t="s">
-        <v>359</v>
+        <v>369</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
@@ -6576,10 +6594,10 @@
         <v>3</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>173</v>
+        <v>15</v>
       </c>
       <c r="F197" s="1" t="s">
         <v>5</v>
@@ -6596,30 +6614,30 @@
         <v>3</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>422</v>
+        <v>405</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>4</v>
+        <v>156</v>
       </c>
       <c r="F198" s="1" t="s">
-        <v>5</v>
+        <v>369</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="B199" s="1" t="s">
         <v>423</v>
       </c>
-      <c r="B199" s="1" t="s">
-        <v>424</v>
-      </c>
       <c r="C199" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>422</v>
+        <v>405</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>18</v>
+        <v>173</v>
       </c>
       <c r="F199" s="1" t="s">
         <v>5</v>
@@ -6627,19 +6645,19 @@
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="B200" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="B200" s="1" t="s">
+      <c r="C200" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D200" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="C200" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D200" s="1" t="s">
-        <v>422</v>
-      </c>
       <c r="E200" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F200" s="1" t="s">
         <v>5</v>
@@ -6656,10 +6674,10 @@
         <v>3</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F201" s="1" t="s">
         <v>5</v>
@@ -6676,10 +6694,10 @@
         <v>3</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="F202" s="1" t="s">
         <v>5</v>
@@ -6696,13 +6714,13 @@
         <v>3</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F203" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
@@ -6716,13 +6734,13 @@
         <v>3</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F204" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
@@ -6736,13 +6754,13 @@
         <v>3</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F205" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
@@ -6756,10 +6774,10 @@
         <v>3</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>156</v>
+        <v>34</v>
       </c>
       <c r="F206" s="1" t="s">
         <v>12</v>
@@ -6776,10 +6794,10 @@
         <v>3</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>173</v>
+        <v>15</v>
       </c>
       <c r="F207" s="1" t="s">
         <v>12</v>
@@ -6796,13 +6814,13 @@
         <v>3</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>176</v>
+        <v>156</v>
       </c>
       <c r="F208" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
@@ -6816,53 +6834,53 @@
         <v>3</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>445</v>
+        <v>426</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>4</v>
+        <v>173</v>
       </c>
       <c r="F209" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="B210" s="1" t="s">
         <v>446</v>
       </c>
-      <c r="B210" s="1" t="s">
-        <v>447</v>
-      </c>
       <c r="C210" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>445</v>
+        <v>426</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>18</v>
+        <v>176</v>
       </c>
       <c r="F210" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="B211" s="1" t="s">
         <v>448</v>
       </c>
-      <c r="B211" s="1" t="s">
+      <c r="C211" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D211" s="1" t="s">
         <v>449</v>
       </c>
-      <c r="C211" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D211" s="1" t="s">
-        <v>445</v>
-      </c>
       <c r="E211" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F211" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
@@ -6876,13 +6894,13 @@
         <v>3</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F212" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
@@ -6896,10 +6914,10 @@
         <v>3</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="F213" s="1" t="s">
         <v>12</v>
@@ -6916,13 +6934,13 @@
         <v>3</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F214" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
@@ -6936,73 +6954,73 @@
         <v>3</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F215" s="1" t="s">
-        <v>458</v>
+        <v>5</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="B216" s="1" t="s">
         <v>459</v>
       </c>
-      <c r="B216" s="1" t="s">
-        <v>460</v>
-      </c>
       <c r="C216" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F216" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="B217" s="1" t="s">
         <v>461</v>
       </c>
-      <c r="B217" s="1" t="s">
-        <v>462</v>
-      </c>
       <c r="C217" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>173</v>
+        <v>34</v>
       </c>
       <c r="F217" s="1" t="s">
-        <v>83</v>
+        <v>12</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="B218" s="1" t="s">
         <v>463</v>
       </c>
-      <c r="B218" s="1" t="s">
+      <c r="C218" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D218" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="E218" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F218" s="1" t="s">
         <v>464</v>
-      </c>
-      <c r="C218" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D218" s="1" t="s">
-        <v>445</v>
-      </c>
-      <c r="E218" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="F218" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
@@ -7016,73 +7034,73 @@
         <v>3</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>467</v>
+        <v>449</v>
       </c>
       <c r="E219" s="1" t="s">
-        <v>4</v>
+        <v>156</v>
       </c>
       <c r="F219" s="1" t="s">
-        <v>468</v>
+        <v>5</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C220" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>467</v>
+        <v>449</v>
       </c>
       <c r="E220" s="1" t="s">
-        <v>8</v>
+        <v>176</v>
       </c>
       <c r="F220" s="1" t="s">
-        <v>23</v>
+        <v>83</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="B221" s="1" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="C221" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>467</v>
+        <v>449</v>
       </c>
       <c r="E221" s="1" t="s">
-        <v>26</v>
+        <v>179</v>
       </c>
       <c r="F221" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="B222" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="C222" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D222" s="1" t="s">
         <v>473</v>
       </c>
-      <c r="B222" s="1" t="s">
+      <c r="E222" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F222" s="1" t="s">
         <v>474</v>
-      </c>
-      <c r="C222" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D222" s="1" t="s">
-        <v>467</v>
-      </c>
-      <c r="E222" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F222" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
@@ -7096,10 +7114,10 @@
         <v>3</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>467</v>
+        <v>473</v>
       </c>
       <c r="E223" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F223" s="1" t="s">
         <v>23</v>
@@ -7116,13 +7134,13 @@
         <v>3</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>467</v>
+        <v>473</v>
       </c>
       <c r="E224" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="F224" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
@@ -7136,13 +7154,13 @@
         <v>3</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>467</v>
+        <v>473</v>
       </c>
       <c r="E225" s="1" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="F225" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
@@ -7156,10 +7174,10 @@
         <v>3</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>467</v>
+        <v>473</v>
       </c>
       <c r="E226" s="1" t="s">
-        <v>156</v>
+        <v>11</v>
       </c>
       <c r="F226" s="1" t="s">
         <v>23</v>
@@ -7176,13 +7194,13 @@
         <v>3</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>467</v>
+        <v>473</v>
       </c>
       <c r="E227" s="1" t="s">
-        <v>173</v>
+        <v>34</v>
       </c>
       <c r="F227" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
@@ -7196,13 +7214,13 @@
         <v>3</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>467</v>
+        <v>473</v>
       </c>
       <c r="E228" s="1" t="s">
-        <v>176</v>
+        <v>15</v>
       </c>
       <c r="F228" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
@@ -7216,10 +7234,10 @@
         <v>3</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>467</v>
+        <v>473</v>
       </c>
       <c r="E229" s="1" t="s">
-        <v>179</v>
+        <v>156</v>
       </c>
       <c r="F229" s="1" t="s">
         <v>23</v>
@@ -7236,10 +7254,10 @@
         <v>3</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>467</v>
+        <v>473</v>
       </c>
       <c r="E230" s="1" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="F230" s="1" t="s">
         <v>23</v>
@@ -7256,73 +7274,73 @@
         <v>3</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>493</v>
+        <v>473</v>
       </c>
       <c r="E231" s="1" t="s">
-        <v>4</v>
+        <v>176</v>
       </c>
       <c r="F231" s="1" t="s">
-        <v>494</v>
+        <v>23</v>
       </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A232" s="1" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="C232" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>493</v>
+        <v>473</v>
       </c>
       <c r="E232" s="1" t="s">
-        <v>4</v>
+        <v>179</v>
       </c>
       <c r="F232" s="1" t="s">
-        <v>494</v>
+        <v>23</v>
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A233" s="1" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="B233" s="1" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="C233" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>493</v>
+        <v>473</v>
       </c>
       <c r="E233" s="1" t="s">
-        <v>4</v>
+        <v>182</v>
       </c>
       <c r="F233" s="1" t="s">
-        <v>494</v>
+        <v>23</v>
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A234" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="B234" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="C234" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D234" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="B234" s="1" t="s">
+      <c r="E234" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F234" s="1" t="s">
         <v>500</v>
-      </c>
-      <c r="C234" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D234" s="1" t="s">
-        <v>493</v>
-      </c>
-      <c r="E234" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F234" s="1" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.25">
@@ -7336,13 +7354,13 @@
         <v>3</v>
       </c>
       <c r="D235" s="1" t="s">
-        <v>493</v>
+        <v>499</v>
       </c>
       <c r="E235" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F235" s="1" t="s">
-        <v>83</v>
+        <v>500</v>
       </c>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.25">
@@ -7356,13 +7374,13 @@
         <v>3</v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>493</v>
+        <v>499</v>
       </c>
       <c r="E236" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F236" s="1" t="s">
-        <v>494</v>
+        <v>500</v>
       </c>
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.25">
@@ -7376,10 +7394,10 @@
         <v>3</v>
       </c>
       <c r="D237" s="1" t="s">
-        <v>493</v>
+        <v>499</v>
       </c>
       <c r="E237" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F237" s="1" t="s">
         <v>83</v>
@@ -7396,10 +7414,10 @@
         <v>3</v>
       </c>
       <c r="D238" s="1" t="s">
-        <v>493</v>
+        <v>499</v>
       </c>
       <c r="E238" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F238" s="1" t="s">
         <v>83</v>
@@ -7416,13 +7434,13 @@
         <v>3</v>
       </c>
       <c r="D239" s="1" t="s">
-        <v>493</v>
+        <v>499</v>
       </c>
       <c r="E239" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F239" s="1" t="s">
-        <v>5</v>
+        <v>500</v>
       </c>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.25">
@@ -7436,13 +7454,13 @@
         <v>3</v>
       </c>
       <c r="D240" s="1" t="s">
-        <v>493</v>
+        <v>499</v>
       </c>
       <c r="E240" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F240" s="1" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.25">
@@ -7456,13 +7474,13 @@
         <v>3</v>
       </c>
       <c r="D241" s="1" t="s">
-        <v>493</v>
+        <v>499</v>
       </c>
       <c r="E241" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F241" s="1" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.25">
@@ -7476,10 +7494,10 @@
         <v>3</v>
       </c>
       <c r="D242" s="1" t="s">
-        <v>493</v>
+        <v>499</v>
       </c>
       <c r="E242" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F242" s="1" t="s">
         <v>5</v>
@@ -7496,10 +7514,10 @@
         <v>3</v>
       </c>
       <c r="D243" s="1" t="s">
-        <v>493</v>
+        <v>499</v>
       </c>
       <c r="E243" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F243" s="1" t="s">
         <v>5</v>
@@ -7516,10 +7534,10 @@
         <v>3</v>
       </c>
       <c r="D244" s="1" t="s">
-        <v>493</v>
+        <v>499</v>
       </c>
       <c r="E244" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F244" s="1" t="s">
         <v>5</v>
@@ -7536,10 +7554,10 @@
         <v>3</v>
       </c>
       <c r="D245" s="1" t="s">
-        <v>493</v>
+        <v>499</v>
       </c>
       <c r="E245" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F245" s="1" t="s">
         <v>5</v>
@@ -7556,10 +7574,10 @@
         <v>3</v>
       </c>
       <c r="D246" s="1" t="s">
-        <v>493</v>
+        <v>499</v>
       </c>
       <c r="E246" s="1" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F246" s="1" t="s">
         <v>5</v>
@@ -7576,10 +7594,10 @@
         <v>3</v>
       </c>
       <c r="D247" s="1" t="s">
-        <v>493</v>
+        <v>499</v>
       </c>
       <c r="E247" s="1" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F247" s="1" t="s">
         <v>5</v>
@@ -7596,10 +7614,10 @@
         <v>3</v>
       </c>
       <c r="D248" s="1" t="s">
-        <v>493</v>
+        <v>499</v>
       </c>
       <c r="E248" s="1" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F248" s="1" t="s">
         <v>5</v>
@@ -7616,10 +7634,10 @@
         <v>3</v>
       </c>
       <c r="D249" s="1" t="s">
-        <v>493</v>
+        <v>499</v>
       </c>
       <c r="E249" s="1" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="F249" s="1" t="s">
         <v>5</v>
@@ -7636,10 +7654,10 @@
         <v>3</v>
       </c>
       <c r="D250" s="1" t="s">
-        <v>493</v>
+        <v>499</v>
       </c>
       <c r="E250" s="1" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="F250" s="1" t="s">
         <v>5</v>
@@ -7656,10 +7674,10 @@
         <v>3</v>
       </c>
       <c r="D251" s="1" t="s">
-        <v>493</v>
+        <v>499</v>
       </c>
       <c r="E251" s="1" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="F251" s="1" t="s">
         <v>5</v>
@@ -7676,10 +7694,10 @@
         <v>3</v>
       </c>
       <c r="D252" s="1" t="s">
-        <v>493</v>
+        <v>499</v>
       </c>
       <c r="E252" s="1" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F252" s="1" t="s">
         <v>5</v>
@@ -7696,10 +7714,10 @@
         <v>3</v>
       </c>
       <c r="D253" s="1" t="s">
-        <v>539</v>
+        <v>499</v>
       </c>
       <c r="E253" s="1" t="s">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="F253" s="1" t="s">
         <v>5</v>
@@ -7707,19 +7725,19 @@
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A254" s="1" t="s">
+        <v>539</v>
+      </c>
+      <c r="B254" s="1" t="s">
         <v>540</v>
       </c>
-      <c r="B254" s="1" t="s">
-        <v>541</v>
-      </c>
       <c r="C254" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D254" s="1" t="s">
-        <v>539</v>
+        <v>499</v>
       </c>
       <c r="E254" s="1" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="F254" s="1" t="s">
         <v>5</v>
@@ -7727,19 +7745,19 @@
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A255" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="B255" s="1" t="s">
         <v>542</v>
       </c>
-      <c r="B255" s="1" t="s">
-        <v>543</v>
-      </c>
       <c r="C255" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D255" s="1" t="s">
-        <v>539</v>
+        <v>499</v>
       </c>
       <c r="E255" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F255" s="1" t="s">
         <v>5</v>
@@ -7747,22 +7765,22 @@
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A256" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="B256" s="1" t="s">
         <v>544</v>
       </c>
-      <c r="B256" s="1" t="s">
+      <c r="C256" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D256" s="1" t="s">
         <v>545</v>
       </c>
-      <c r="C256" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D256" s="1" t="s">
-        <v>539</v>
-      </c>
       <c r="E256" s="1" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="F256" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.25">
@@ -7776,13 +7794,13 @@
         <v>3</v>
       </c>
       <c r="D257" s="1" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="E257" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="F257" s="1" t="s">
-        <v>83</v>
+        <v>5</v>
       </c>
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.25">
@@ -7796,10 +7814,10 @@
         <v>3</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>550</v>
+        <v>545</v>
       </c>
       <c r="E258" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F258" s="1" t="s">
         <v>5</v>
@@ -7807,62 +7825,62 @@
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A259" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="B259" s="1" t="s">
         <v>551</v>
       </c>
-      <c r="B259" s="1" t="s">
-        <v>552</v>
-      </c>
       <c r="C259" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>550</v>
+        <v>545</v>
       </c>
       <c r="E259" s="1" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F259" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A260" s="1" t="s">
+        <v>552</v>
+      </c>
+      <c r="B260" s="1" t="s">
         <v>553</v>
       </c>
-      <c r="B260" s="1" t="s">
-        <v>554</v>
-      </c>
       <c r="C260" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>550</v>
+        <v>545</v>
       </c>
       <c r="E260" s="1" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="F260" s="1" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A261" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="B261" s="1" t="s">
         <v>555</v>
       </c>
-      <c r="B261" s="1" t="s">
+      <c r="C261" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D261" s="1" t="s">
         <v>556</v>
       </c>
-      <c r="C261" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D261" s="1" t="s">
-        <v>550</v>
-      </c>
       <c r="E261" s="1" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="F261" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.25">
@@ -7876,13 +7894,13 @@
         <v>3</v>
       </c>
       <c r="D262" s="1" t="s">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="E262" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="F262" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.25">
@@ -7896,10 +7914,10 @@
         <v>3</v>
       </c>
       <c r="D263" s="1" t="s">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="E263" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F263" s="1" t="s">
         <v>5</v>
@@ -7916,13 +7934,13 @@
         <v>3</v>
       </c>
       <c r="D264" s="1" t="s">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="E264" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="F264" s="1" t="s">
-        <v>83</v>
+        <v>23</v>
       </c>
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.25">
@@ -7936,30 +7954,30 @@
         <v>3</v>
       </c>
       <c r="D265" s="1" t="s">
-        <v>565</v>
+        <v>556</v>
       </c>
       <c r="E265" s="1" t="s">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="F265" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A266" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="B266" s="1" t="s">
         <v>566</v>
       </c>
-      <c r="B266" s="1" t="s">
-        <v>567</v>
-      </c>
       <c r="C266" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D266" s="1" t="s">
-        <v>565</v>
+        <v>556</v>
       </c>
       <c r="E266" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F266" s="1" t="s">
         <v>5</v>
@@ -7967,42 +7985,42 @@
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A267" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="B267" s="1" t="s">
         <v>568</v>
       </c>
-      <c r="B267" s="1" t="s">
-        <v>569</v>
-      </c>
       <c r="C267" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D267" s="1" t="s">
-        <v>565</v>
+        <v>556</v>
       </c>
       <c r="E267" s="1" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="F267" s="1" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A268" s="1" t="s">
+        <v>569</v>
+      </c>
+      <c r="B268" s="1" t="s">
         <v>570</v>
       </c>
-      <c r="B268" s="1" t="s">
+      <c r="C268" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D268" s="1" t="s">
         <v>571</v>
       </c>
-      <c r="C268" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D268" s="1" t="s">
-        <v>565</v>
-      </c>
       <c r="E268" s="1" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="F268" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.25">
@@ -8016,13 +8034,13 @@
         <v>3</v>
       </c>
       <c r="D269" s="1" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="E269" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="F269" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.25">
@@ -8036,13 +8054,13 @@
         <v>3</v>
       </c>
       <c r="D270" s="1" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="E270" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F270" s="1" t="s">
-        <v>83</v>
+        <v>5</v>
       </c>
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.25">
@@ -8056,30 +8074,30 @@
         <v>3</v>
       </c>
       <c r="D271" s="1" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="E271" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="F271" s="1" t="s">
-        <v>578</v>
+        <v>23</v>
       </c>
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A272" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="B272" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="B272" s="1" t="s">
-        <v>580</v>
-      </c>
       <c r="C272" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D272" s="1" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="E272" s="1" t="s">
-        <v>156</v>
+        <v>29</v>
       </c>
       <c r="F272" s="1" t="s">
         <v>23</v>
@@ -8087,42 +8105,42 @@
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A273" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="B273" s="1" t="s">
         <v>581</v>
       </c>
-      <c r="B273" s="1" t="s">
-        <v>582</v>
-      </c>
       <c r="C273" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D273" s="1" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="E273" s="1" t="s">
-        <v>173</v>
+        <v>11</v>
       </c>
       <c r="F273" s="1" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A274" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="B274" s="1" t="s">
         <v>583</v>
       </c>
-      <c r="B274" s="1" t="s">
+      <c r="C274" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D274" s="1" t="s">
+        <v>571</v>
+      </c>
+      <c r="E274" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F274" s="1" t="s">
         <v>584</v>
-      </c>
-      <c r="C274" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D274" s="1" t="s">
-        <v>565</v>
-      </c>
-      <c r="E274" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="F274" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.25">
@@ -8136,70 +8154,70 @@
         <v>3</v>
       </c>
       <c r="D275" s="1" t="s">
-        <v>587</v>
+        <v>571</v>
       </c>
       <c r="E275" s="1" t="s">
-        <v>4</v>
+        <v>156</v>
       </c>
       <c r="F275" s="1" t="s">
-        <v>83</v>
+        <v>23</v>
       </c>
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A276" s="1" t="s">
+        <v>587</v>
+      </c>
+      <c r="B276" s="1" t="s">
         <v>588</v>
       </c>
-      <c r="B276" s="1" t="s">
-        <v>589</v>
-      </c>
       <c r="C276" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D276" s="1" t="s">
-        <v>587</v>
+        <v>571</v>
       </c>
       <c r="E276" s="1" t="s">
-        <v>18</v>
+        <v>173</v>
       </c>
       <c r="F276" s="1" t="s">
-        <v>83</v>
+        <v>5</v>
       </c>
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A277" s="1" t="s">
+        <v>589</v>
+      </c>
+      <c r="B277" s="1" t="s">
         <v>590</v>
       </c>
-      <c r="B277" s="1" t="s">
-        <v>591</v>
-      </c>
       <c r="C277" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D277" s="1" t="s">
-        <v>587</v>
+        <v>571</v>
       </c>
       <c r="E277" s="1" t="s">
-        <v>8</v>
+        <v>176</v>
       </c>
       <c r="F277" s="1" t="s">
-        <v>83</v>
+        <v>12</v>
       </c>
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A278" s="1" t="s">
+        <v>591</v>
+      </c>
+      <c r="B278" s="1" t="s">
         <v>592</v>
       </c>
-      <c r="B278" s="1" t="s">
+      <c r="C278" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D278" s="1" t="s">
         <v>593</v>
       </c>
-      <c r="C278" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D278" s="1" t="s">
-        <v>587</v>
-      </c>
       <c r="E278" s="1" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="F278" s="1" t="s">
         <v>83</v>
@@ -8216,30 +8234,30 @@
         <v>3</v>
       </c>
       <c r="D279" s="1" t="s">
-        <v>587</v>
+        <v>593</v>
       </c>
       <c r="E279" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="F279" s="1" t="s">
-        <v>596</v>
+        <v>83</v>
       </c>
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A280" s="1" t="s">
+        <v>596</v>
+      </c>
+      <c r="B280" s="1" t="s">
         <v>597</v>
       </c>
-      <c r="B280" s="1" t="s">
-        <v>598</v>
-      </c>
       <c r="C280" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D280" s="1" t="s">
-        <v>587</v>
+        <v>593</v>
       </c>
       <c r="E280" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F280" s="1" t="s">
         <v>83</v>
@@ -8247,19 +8265,19 @@
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A281" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="B281" s="1" t="s">
         <v>599</v>
       </c>
-      <c r="B281" s="1" t="s">
-        <v>600</v>
-      </c>
       <c r="C281" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D281" s="1" t="s">
-        <v>587</v>
+        <v>593</v>
       </c>
       <c r="E281" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="F281" s="1" t="s">
         <v>83</v>
@@ -8267,22 +8285,22 @@
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A282" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="B282" s="1" t="s">
         <v>601</v>
       </c>
-      <c r="B282" s="1" t="s">
+      <c r="C282" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D282" s="1" t="s">
+        <v>593</v>
+      </c>
+      <c r="E282" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F282" s="1" t="s">
         <v>602</v>
-      </c>
-      <c r="C282" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D282" s="1" t="s">
-        <v>587</v>
-      </c>
-      <c r="E282" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F282" s="1" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.25">
@@ -8296,70 +8314,70 @@
         <v>3</v>
       </c>
       <c r="D283" s="1" t="s">
-        <v>605</v>
+        <v>593</v>
       </c>
       <c r="E283" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F283" s="1" t="s">
-        <v>12</v>
+        <v>83</v>
       </c>
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A284" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="B284" s="1" t="s">
         <v>606</v>
       </c>
-      <c r="B284" s="1" t="s">
-        <v>607</v>
-      </c>
       <c r="C284" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D284" s="1" t="s">
-        <v>605</v>
+        <v>593</v>
       </c>
       <c r="E284" s="1" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="F284" s="1" t="s">
-        <v>12</v>
+        <v>83</v>
       </c>
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A285" s="1" t="s">
+        <v>607</v>
+      </c>
+      <c r="B285" s="1" t="s">
         <v>608</v>
       </c>
-      <c r="B285" s="1" t="s">
-        <v>609</v>
-      </c>
       <c r="C285" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D285" s="1" t="s">
-        <v>605</v>
+        <v>593</v>
       </c>
       <c r="E285" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F285" s="1" t="s">
-        <v>12</v>
+        <v>83</v>
       </c>
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A286" s="1" t="s">
+        <v>609</v>
+      </c>
+      <c r="B286" s="1" t="s">
         <v>610</v>
       </c>
-      <c r="B286" s="1" t="s">
+      <c r="C286" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D286" s="1" t="s">
         <v>611</v>
       </c>
-      <c r="C286" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D286" s="1" t="s">
-        <v>605</v>
-      </c>
       <c r="E286" s="1" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="F286" s="1" t="s">
         <v>12</v>
@@ -8376,13 +8394,13 @@
         <v>3</v>
       </c>
       <c r="D287" s="1" t="s">
-        <v>605</v>
+        <v>611</v>
       </c>
       <c r="E287" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="F287" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.25">
@@ -8396,13 +8414,13 @@
         <v>3</v>
       </c>
       <c r="D288" s="1" t="s">
-        <v>605</v>
+        <v>611</v>
       </c>
       <c r="E288" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F288" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.25">
@@ -8416,13 +8434,13 @@
         <v>3</v>
       </c>
       <c r="D289" s="1" t="s">
-        <v>605</v>
+        <v>611</v>
       </c>
       <c r="E289" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="F289" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.25">
@@ -8436,13 +8454,13 @@
         <v>3</v>
       </c>
       <c r="D290" s="1" t="s">
-        <v>605</v>
+        <v>611</v>
       </c>
       <c r="E290" s="1" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="F290" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.25">
@@ -8456,50 +8474,50 @@
         <v>3</v>
       </c>
       <c r="D291" s="1" t="s">
-        <v>622</v>
+        <v>611</v>
       </c>
       <c r="E291" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F291" s="1" t="s">
-        <v>623</v>
+        <v>23</v>
       </c>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A292" s="1" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="B292" s="1" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="C292" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D292" s="1" t="s">
-        <v>622</v>
+        <v>611</v>
       </c>
       <c r="E292" s="1" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="F292" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A293" s="1" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="B293" s="1" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="C293" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D293" s="1" t="s">
-        <v>622</v>
+        <v>611</v>
       </c>
       <c r="E293" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F293" s="1" t="s">
         <v>12</v>
@@ -8507,22 +8525,22 @@
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A294" s="1" t="s">
+        <v>626</v>
+      </c>
+      <c r="B294" s="1" t="s">
+        <v>627</v>
+      </c>
+      <c r="C294" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D294" s="1" t="s">
         <v>628</v>
       </c>
-      <c r="B294" s="1" t="s">
+      <c r="E294" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F294" s="1" t="s">
         <v>629</v>
-      </c>
-      <c r="C294" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D294" s="1" t="s">
-        <v>622</v>
-      </c>
-      <c r="E294" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F294" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.25">
@@ -8536,10 +8554,10 @@
         <v>3</v>
       </c>
       <c r="D295" s="1" t="s">
-        <v>622</v>
+        <v>628</v>
       </c>
       <c r="E295" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="F295" s="1" t="s">
         <v>12</v>
@@ -8556,13 +8574,13 @@
         <v>3</v>
       </c>
       <c r="D296" s="1" t="s">
-        <v>622</v>
+        <v>628</v>
       </c>
       <c r="E296" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F296" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.25">
@@ -8576,10 +8594,10 @@
         <v>3</v>
       </c>
       <c r="D297" s="1" t="s">
-        <v>622</v>
+        <v>628</v>
       </c>
       <c r="E297" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="F297" s="1" t="s">
         <v>12</v>
@@ -8596,10 +8614,10 @@
         <v>3</v>
       </c>
       <c r="D298" s="1" t="s">
-        <v>622</v>
+        <v>628</v>
       </c>
       <c r="E298" s="1" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="F298" s="1" t="s">
         <v>12</v>
@@ -8616,13 +8634,13 @@
         <v>3</v>
       </c>
       <c r="D299" s="1" t="s">
-        <v>622</v>
+        <v>628</v>
       </c>
       <c r="E299" s="1" t="s">
-        <v>156</v>
+        <v>11</v>
       </c>
       <c r="F299" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.25">
@@ -8636,10 +8654,10 @@
         <v>3</v>
       </c>
       <c r="D300" s="1" t="s">
-        <v>622</v>
+        <v>628</v>
       </c>
       <c r="E300" s="1" t="s">
-        <v>173</v>
+        <v>34</v>
       </c>
       <c r="F300" s="1" t="s">
         <v>12</v>
@@ -8656,13 +8674,13 @@
         <v>3</v>
       </c>
       <c r="D301" s="1" t="s">
-        <v>622</v>
+        <v>628</v>
       </c>
       <c r="E301" s="1" t="s">
-        <v>176</v>
+        <v>15</v>
       </c>
       <c r="F301" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.25">
@@ -8676,10 +8694,10 @@
         <v>3</v>
       </c>
       <c r="D302" s="1" t="s">
-        <v>622</v>
+        <v>628</v>
       </c>
       <c r="E302" s="1" t="s">
-        <v>179</v>
+        <v>156</v>
       </c>
       <c r="F302" s="1" t="s">
         <v>12</v>
@@ -8696,13 +8714,13 @@
         <v>3</v>
       </c>
       <c r="D303" s="1" t="s">
-        <v>622</v>
+        <v>628</v>
       </c>
       <c r="E303" s="1" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="F303" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="304" spans="1:6" x14ac:dyDescent="0.25">
@@ -8716,13 +8734,13 @@
         <v>3</v>
       </c>
       <c r="D304" s="1" t="s">
-        <v>622</v>
+        <v>628</v>
       </c>
       <c r="E304" s="1" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="F304" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="305" spans="1:6" x14ac:dyDescent="0.25">
@@ -8736,10 +8754,10 @@
         <v>3</v>
       </c>
       <c r="D305" s="1" t="s">
-        <v>652</v>
+        <v>628</v>
       </c>
       <c r="E305" s="1" t="s">
-        <v>4</v>
+        <v>179</v>
       </c>
       <c r="F305" s="1" t="s">
         <v>12</v>
@@ -8747,39 +8765,39 @@
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A306" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="B306" s="1" t="s">
         <v>653</v>
       </c>
-      <c r="B306" s="1" t="s">
-        <v>654</v>
-      </c>
       <c r="C306" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D306" s="1" t="s">
-        <v>652</v>
+        <v>628</v>
       </c>
       <c r="E306" s="1" t="s">
-        <v>18</v>
+        <v>182</v>
       </c>
       <c r="F306" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A307" s="1" t="s">
+        <v>654</v>
+      </c>
+      <c r="B307" s="1" t="s">
         <v>655</v>
       </c>
-      <c r="B307" s="1" t="s">
-        <v>656</v>
-      </c>
       <c r="C307" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D307" s="1" t="s">
-        <v>652</v>
+        <v>628</v>
       </c>
       <c r="E307" s="1" t="s">
-        <v>8</v>
+        <v>185</v>
       </c>
       <c r="F307" s="1" t="s">
         <v>12</v>
@@ -8787,19 +8805,19 @@
     </row>
     <row r="308" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A308" s="1" t="s">
+        <v>656</v>
+      </c>
+      <c r="B308" s="1" t="s">
         <v>657</v>
       </c>
-      <c r="B308" s="1" t="s">
+      <c r="C308" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D308" s="1" t="s">
         <v>658</v>
       </c>
-      <c r="C308" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D308" s="1" t="s">
-        <v>652</v>
-      </c>
       <c r="E308" s="1" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="F308" s="1" t="s">
         <v>12</v>
@@ -8816,13 +8834,13 @@
         <v>3</v>
       </c>
       <c r="D309" s="1" t="s">
-        <v>652</v>
+        <v>658</v>
       </c>
       <c r="E309" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="F309" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.25">
@@ -8836,10 +8854,10 @@
         <v>3</v>
       </c>
       <c r="D310" s="1" t="s">
-        <v>652</v>
+        <v>658</v>
       </c>
       <c r="E310" s="1" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="F310" s="1" t="s">
         <v>12</v>
@@ -8856,10 +8874,10 @@
         <v>3</v>
       </c>
       <c r="D311" s="1" t="s">
-        <v>652</v>
+        <v>658</v>
       </c>
       <c r="E311" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F311" s="1" t="s">
         <v>12</v>
@@ -8876,13 +8894,13 @@
         <v>3</v>
       </c>
       <c r="D312" s="1" t="s">
-        <v>652</v>
+        <v>658</v>
       </c>
       <c r="E312" s="1" t="s">
-        <v>156</v>
+        <v>29</v>
       </c>
       <c r="F312" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="313" spans="1:6" x14ac:dyDescent="0.25">
@@ -8896,50 +8914,50 @@
         <v>3</v>
       </c>
       <c r="D313" s="1" t="s">
-        <v>669</v>
+        <v>658</v>
       </c>
       <c r="E313" s="1" t="s">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="F313" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="314" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A314" s="1" t="s">
+        <v>669</v>
+      </c>
+      <c r="B314" s="1" t="s">
         <v>670</v>
       </c>
-      <c r="B314" s="1" t="s">
-        <v>671</v>
-      </c>
       <c r="C314" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D314" s="1" t="s">
-        <v>669</v>
+        <v>658</v>
       </c>
       <c r="E314" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F314" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="315" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A315" s="1" t="s">
+        <v>671</v>
+      </c>
+      <c r="B315" s="1" t="s">
         <v>672</v>
       </c>
-      <c r="B315" s="1" t="s">
-        <v>673</v>
-      </c>
       <c r="C315" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D315" s="1" t="s">
-        <v>669</v>
+        <v>658</v>
       </c>
       <c r="E315" s="1" t="s">
-        <v>8</v>
+        <v>156</v>
       </c>
       <c r="F315" s="1" t="s">
         <v>23</v>
@@ -8947,22 +8965,22 @@
     </row>
     <row r="316" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A316" s="1" t="s">
+        <v>673</v>
+      </c>
+      <c r="B316" s="1" t="s">
         <v>674</v>
       </c>
-      <c r="B316" s="1" t="s">
+      <c r="C316" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D316" s="1" t="s">
         <v>675</v>
       </c>
-      <c r="C316" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D316" s="1" t="s">
-        <v>669</v>
-      </c>
       <c r="E316" s="1" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="F316" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="317" spans="1:6" x14ac:dyDescent="0.25">
@@ -8976,13 +8994,13 @@
         <v>3</v>
       </c>
       <c r="D317" s="1" t="s">
-        <v>669</v>
+        <v>675</v>
       </c>
       <c r="E317" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="F317" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="318" spans="1:6" x14ac:dyDescent="0.25">
@@ -8996,13 +9014,13 @@
         <v>3</v>
       </c>
       <c r="D318" s="1" t="s">
-        <v>669</v>
+        <v>675</v>
       </c>
       <c r="E318" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F318" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="319" spans="1:6" x14ac:dyDescent="0.25">
@@ -9016,10 +9034,10 @@
         <v>3</v>
       </c>
       <c r="D319" s="1" t="s">
-        <v>669</v>
+        <v>675</v>
       </c>
       <c r="E319" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="F319" s="1" t="s">
         <v>12</v>
@@ -9036,10 +9054,10 @@
         <v>3</v>
       </c>
       <c r="D320" s="1" t="s">
-        <v>669</v>
+        <v>675</v>
       </c>
       <c r="E320" s="1" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="F320" s="1" t="s">
         <v>12</v>
@@ -9056,10 +9074,10 @@
         <v>3</v>
       </c>
       <c r="D321" s="1" t="s">
-        <v>669</v>
+        <v>675</v>
       </c>
       <c r="E321" s="1" t="s">
-        <v>156</v>
+        <v>11</v>
       </c>
       <c r="F321" s="1" t="s">
         <v>12</v>
@@ -9076,10 +9094,10 @@
         <v>3</v>
       </c>
       <c r="D322" s="1" t="s">
-        <v>688</v>
+        <v>675</v>
       </c>
       <c r="E322" s="1" t="s">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="F322" s="1" t="s">
         <v>12</v>
@@ -9087,19 +9105,19 @@
     </row>
     <row r="323" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A323" s="1" t="s">
+        <v>688</v>
+      </c>
+      <c r="B323" s="1" t="s">
         <v>689</v>
       </c>
-      <c r="B323" s="1" t="s">
-        <v>690</v>
-      </c>
       <c r="C323" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D323" s="1" t="s">
-        <v>688</v>
+        <v>675</v>
       </c>
       <c r="E323" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F323" s="1" t="s">
         <v>12</v>
@@ -9107,42 +9125,42 @@
     </row>
     <row r="324" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A324" s="1" t="s">
+        <v>690</v>
+      </c>
+      <c r="B324" s="1" t="s">
         <v>691</v>
       </c>
-      <c r="B324" s="1" t="s">
-        <v>692</v>
-      </c>
       <c r="C324" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D324" s="1" t="s">
-        <v>688</v>
+        <v>675</v>
       </c>
       <c r="E324" s="1" t="s">
-        <v>8</v>
+        <v>156</v>
       </c>
       <c r="F324" s="1" t="s">
-        <v>83</v>
+        <v>12</v>
       </c>
     </row>
     <row r="325" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A325" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="B325" s="1" t="s">
         <v>693</v>
       </c>
-      <c r="B325" s="1" t="s">
+      <c r="C325" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D325" s="1" t="s">
         <v>694</v>
       </c>
-      <c r="C325" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D325" s="1" t="s">
-        <v>688</v>
-      </c>
       <c r="E325" s="1" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="F325" s="1" t="s">
-        <v>468</v>
+        <v>12</v>
       </c>
     </row>
     <row r="326" spans="1:6" x14ac:dyDescent="0.25">
@@ -9156,10 +9174,10 @@
         <v>3</v>
       </c>
       <c r="D326" s="1" t="s">
-        <v>688</v>
+        <v>694</v>
       </c>
       <c r="E326" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="F326" s="1" t="s">
         <v>12</v>
@@ -9176,13 +9194,13 @@
         <v>3</v>
       </c>
       <c r="D327" s="1" t="s">
-        <v>688</v>
+        <v>694</v>
       </c>
       <c r="E327" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F327" s="1" t="s">
-        <v>23</v>
+        <v>83</v>
       </c>
     </row>
     <row r="328" spans="1:6" x14ac:dyDescent="0.25">
@@ -9196,30 +9214,30 @@
         <v>3</v>
       </c>
       <c r="D328" s="1" t="s">
-        <v>701</v>
+        <v>694</v>
       </c>
       <c r="E328" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="F328" s="1" t="s">
-        <v>12</v>
+        <v>474</v>
       </c>
     </row>
     <row r="329" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A329" s="1" t="s">
+        <v>701</v>
+      </c>
+      <c r="B329" s="1" t="s">
         <v>702</v>
       </c>
-      <c r="B329" s="1" t="s">
-        <v>703</v>
-      </c>
       <c r="C329" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D329" s="1" t="s">
-        <v>701</v>
+        <v>694</v>
       </c>
       <c r="E329" s="1" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="F329" s="1" t="s">
         <v>12</v>
@@ -9227,42 +9245,42 @@
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A330" s="1" t="s">
+        <v>703</v>
+      </c>
+      <c r="B330" s="1" t="s">
         <v>704</v>
       </c>
-      <c r="B330" s="1" t="s">
-        <v>705</v>
-      </c>
       <c r="C330" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D330" s="1" t="s">
-        <v>701</v>
+        <v>694</v>
       </c>
       <c r="E330" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F330" s="1" t="s">
-        <v>83</v>
+        <v>23</v>
       </c>
     </row>
     <row r="331" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A331" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="B331" s="1" t="s">
         <v>706</v>
       </c>
-      <c r="B331" s="1" t="s">
+      <c r="C331" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D331" s="1" t="s">
         <v>707</v>
       </c>
-      <c r="C331" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D331" s="1" t="s">
-        <v>701</v>
-      </c>
       <c r="E331" s="1" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="F331" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="332" spans="1:6" x14ac:dyDescent="0.25">
@@ -9276,13 +9294,13 @@
         <v>3</v>
       </c>
       <c r="D332" s="1" t="s">
-        <v>701</v>
+        <v>707</v>
       </c>
       <c r="E332" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="F332" s="1" t="s">
-        <v>83</v>
+        <v>12</v>
       </c>
     </row>
     <row r="333" spans="1:6" x14ac:dyDescent="0.25">
@@ -9296,13 +9314,13 @@
         <v>3</v>
       </c>
       <c r="D333" s="1" t="s">
-        <v>701</v>
+        <v>707</v>
       </c>
       <c r="E333" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F333" s="1" t="s">
-        <v>12</v>
+        <v>83</v>
       </c>
     </row>
     <row r="334" spans="1:6" x14ac:dyDescent="0.25">
@@ -9316,30 +9334,30 @@
         <v>3</v>
       </c>
       <c r="D334" s="1" t="s">
-        <v>714</v>
+        <v>707</v>
       </c>
       <c r="E334" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="F334" s="1" t="s">
-        <v>83</v>
+        <v>23</v>
       </c>
     </row>
     <row r="335" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A335" s="1" t="s">
+        <v>714</v>
+      </c>
+      <c r="B335" s="1" t="s">
         <v>715</v>
       </c>
-      <c r="B335" s="1" t="s">
-        <v>716</v>
-      </c>
       <c r="C335" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D335" s="1" t="s">
-        <v>714</v>
+        <v>707</v>
       </c>
       <c r="E335" s="1" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="F335" s="1" t="s">
         <v>83</v>
@@ -9347,39 +9365,39 @@
     </row>
     <row r="336" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A336" s="1" t="s">
+        <v>716</v>
+      </c>
+      <c r="B336" s="1" t="s">
         <v>717</v>
       </c>
-      <c r="B336" s="1" t="s">
-        <v>718</v>
-      </c>
       <c r="C336" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D336" s="1" t="s">
-        <v>714</v>
+        <v>707</v>
       </c>
       <c r="E336" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F336" s="1" t="s">
-        <v>83</v>
+        <v>12</v>
       </c>
     </row>
     <row r="337" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A337" s="1" t="s">
+        <v>718</v>
+      </c>
+      <c r="B337" s="1" t="s">
         <v>719</v>
       </c>
-      <c r="B337" s="1" t="s">
+      <c r="C337" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D337" s="1" t="s">
         <v>720</v>
       </c>
-      <c r="C337" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D337" s="1" t="s">
-        <v>714</v>
-      </c>
       <c r="E337" s="1" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="F337" s="1" t="s">
         <v>83</v>
@@ -9396,10 +9414,10 @@
         <v>3</v>
       </c>
       <c r="D338" s="1" t="s">
-        <v>714</v>
+        <v>720</v>
       </c>
       <c r="E338" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="F338" s="1" t="s">
         <v>83</v>
@@ -9416,10 +9434,10 @@
         <v>3</v>
       </c>
       <c r="D339" s="1" t="s">
-        <v>725</v>
+        <v>720</v>
       </c>
       <c r="E339" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F339" s="1" t="s">
         <v>83</v>
@@ -9427,19 +9445,19 @@
     </row>
     <row r="340" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A340" s="1" t="s">
+        <v>725</v>
+      </c>
+      <c r="B340" s="1" t="s">
         <v>726</v>
       </c>
-      <c r="B340" s="1" t="s">
-        <v>727</v>
-      </c>
       <c r="C340" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D340" s="1" t="s">
-        <v>725</v>
+        <v>720</v>
       </c>
       <c r="E340" s="1" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F340" s="1" t="s">
         <v>83</v>
@@ -9447,19 +9465,19 @@
     </row>
     <row r="341" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A341" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="B341" s="1" t="s">
         <v>728</v>
       </c>
-      <c r="B341" s="1" t="s">
-        <v>729</v>
-      </c>
       <c r="C341" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D341" s="1" t="s">
-        <v>725</v>
+        <v>720</v>
       </c>
       <c r="E341" s="1" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="F341" s="1" t="s">
         <v>83</v>
@@ -9467,19 +9485,19 @@
     </row>
     <row r="342" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A342" s="1" t="s">
+        <v>729</v>
+      </c>
+      <c r="B342" s="1" t="s">
         <v>730</v>
       </c>
-      <c r="B342" s="1" t="s">
+      <c r="C342" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D342" s="1" t="s">
         <v>731</v>
       </c>
-      <c r="C342" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D342" s="1" t="s">
-        <v>725</v>
-      </c>
       <c r="E342" s="1" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="F342" s="1" t="s">
         <v>83</v>
@@ -9496,13 +9514,13 @@
         <v>3</v>
       </c>
       <c r="D343" s="1" t="s">
-        <v>725</v>
+        <v>731</v>
       </c>
       <c r="E343" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="F343" s="1" t="s">
-        <v>12</v>
+        <v>83</v>
       </c>
     </row>
     <row r="344" spans="1:6" x14ac:dyDescent="0.25">
@@ -9516,72 +9534,132 @@
         <v>3</v>
       </c>
       <c r="D344" s="1" t="s">
-        <v>736</v>
+        <v>731</v>
       </c>
       <c r="E344" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F344" s="1" t="s">
-        <v>737</v>
+        <v>83</v>
       </c>
     </row>
     <row r="345" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A345" s="1" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="B345" s="1" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="C345" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D345" s="1" t="s">
-        <v>736</v>
+        <v>731</v>
       </c>
       <c r="E345" s="1" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F345" s="1" t="s">
-        <v>12</v>
+        <v>83</v>
       </c>
     </row>
     <row r="346" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A346" s="1" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="B346" s="1" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="C346" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D346" s="1" t="s">
-        <v>736</v>
+        <v>731</v>
       </c>
       <c r="E346" s="1" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="F346" s="1" t="s">
-        <v>83</v>
+        <v>12</v>
       </c>
     </row>
     <row r="347" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A347" s="1" t="s">
+        <v>740</v>
+      </c>
+      <c r="B347" s="1" t="s">
+        <v>741</v>
+      </c>
+      <c r="C347" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D347" s="1" t="s">
         <v>742</v>
       </c>
-      <c r="B347" s="1" t="s">
+      <c r="E347" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F347" s="1" t="s">
         <v>743</v>
       </c>
-      <c r="C347" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D347" s="1" t="s">
-        <v>736</v>
-      </c>
-      <c r="E347" s="1" t="s">
+    </row>
+    <row r="348" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A348" s="1" t="s">
+        <v>744</v>
+      </c>
+      <c r="B348" s="1" t="s">
+        <v>745</v>
+      </c>
+      <c r="C348" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D348" s="1" t="s">
+        <v>742</v>
+      </c>
+      <c r="E348" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F348" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="349" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A349" s="1" t="s">
+        <v>746</v>
+      </c>
+      <c r="B349" s="1" t="s">
+        <v>747</v>
+      </c>
+      <c r="C349" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D349" s="1" t="s">
+        <v>742</v>
+      </c>
+      <c r="E349" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F349" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="350" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A350" s="1" t="s">
+        <v>748</v>
+      </c>
+      <c r="B350" s="1" t="s">
+        <v>749</v>
+      </c>
+      <c r="C350" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D350" s="1" t="s">
+        <v>742</v>
+      </c>
+      <c r="E350" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F347" s="1" t="s">
+      <c r="F350" s="1" t="s">
         <v>83</v>
       </c>
     </row>

--- a/BFD05D.xlsx
+++ b/BFD05D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2100" uniqueCount="750">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2106" uniqueCount="752">
   <si>
     <t/>
   </si>
@@ -478,7 +478,7 @@
     <t>10006884</t>
   </si>
   <si>
-    <t>ABC MINYAK WIJEN.195</t>
+    <t>ABC MYK WIJEN 195 ML</t>
   </si>
   <si>
     <t>9</t>
@@ -1282,7 +1282,7 @@
     <t>10002350</t>
   </si>
   <si>
-    <t>ABC KCP MANIS TGG275</t>
+    <t>ABC KCP MNS B 275 ML</t>
   </si>
   <si>
     <t>20031907</t>
@@ -1858,7 +1858,7 @@
     <t>10005073</t>
   </si>
   <si>
-    <t>BLUE BAND PCK 200G</t>
+    <t>BLUE BAND PCK 200 G</t>
   </si>
   <si>
     <t>20041164</t>
@@ -1949,6 +1949,12 @@
   </si>
   <si>
     <t>MEG KEJU SRBGN 160G</t>
+  </si>
+  <si>
+    <t>20144283</t>
+  </si>
+  <si>
+    <t>M/CHESE KJU OLES 140</t>
   </si>
   <si>
     <t>20113339</t>
@@ -2653,7 +2659,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F350"/>
+  <dimension ref="A1:F351"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -8740,7 +8746,7 @@
         <v>176</v>
       </c>
       <c r="F304" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="305" spans="1:6" x14ac:dyDescent="0.25">
@@ -8760,7 +8766,7 @@
         <v>179</v>
       </c>
       <c r="F305" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.25">
@@ -8780,7 +8786,7 @@
         <v>182</v>
       </c>
       <c r="F306" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.25">
@@ -8800,7 +8806,7 @@
         <v>185</v>
       </c>
       <c r="F307" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="308" spans="1:6" x14ac:dyDescent="0.25">
@@ -8814,10 +8820,10 @@
         <v>3</v>
       </c>
       <c r="D308" s="1" t="s">
-        <v>658</v>
+        <v>628</v>
       </c>
       <c r="E308" s="1" t="s">
-        <v>4</v>
+        <v>188</v>
       </c>
       <c r="F308" s="1" t="s">
         <v>12</v>
@@ -8825,22 +8831,22 @@
     </row>
     <row r="309" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A309" s="1" t="s">
+        <v>658</v>
+      </c>
+      <c r="B309" s="1" t="s">
         <v>659</v>
       </c>
-      <c r="B309" s="1" t="s">
+      <c r="C309" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D309" s="1" t="s">
         <v>660</v>
       </c>
-      <c r="C309" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D309" s="1" t="s">
-        <v>658</v>
-      </c>
       <c r="E309" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F309" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.25">
@@ -8854,13 +8860,13 @@
         <v>3</v>
       </c>
       <c r="D310" s="1" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="E310" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F310" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.25">
@@ -8874,10 +8880,10 @@
         <v>3</v>
       </c>
       <c r="D311" s="1" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="E311" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F311" s="1" t="s">
         <v>12</v>
@@ -8894,10 +8900,10 @@
         <v>3</v>
       </c>
       <c r="D312" s="1" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="E312" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F312" s="1" t="s">
         <v>12</v>
@@ -8914,10 +8920,10 @@
         <v>3</v>
       </c>
       <c r="D313" s="1" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="E313" s="1" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F313" s="1" t="s">
         <v>12</v>
@@ -8934,10 +8940,10 @@
         <v>3</v>
       </c>
       <c r="D314" s="1" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="E314" s="1" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F314" s="1" t="s">
         <v>12</v>
@@ -8954,13 +8960,13 @@
         <v>3</v>
       </c>
       <c r="D315" s="1" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="E315" s="1" t="s">
-        <v>156</v>
+        <v>15</v>
       </c>
       <c r="F315" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="316" spans="1:6" x14ac:dyDescent="0.25">
@@ -8974,10 +8980,10 @@
         <v>3</v>
       </c>
       <c r="D316" s="1" t="s">
-        <v>675</v>
+        <v>660</v>
       </c>
       <c r="E316" s="1" t="s">
-        <v>4</v>
+        <v>156</v>
       </c>
       <c r="F316" s="1" t="s">
         <v>23</v>
@@ -8985,19 +8991,19 @@
     </row>
     <row r="317" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A317" s="1" t="s">
+        <v>675</v>
+      </c>
+      <c r="B317" s="1" t="s">
         <v>676</v>
       </c>
-      <c r="B317" s="1" t="s">
+      <c r="C317" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D317" s="1" t="s">
         <v>677</v>
       </c>
-      <c r="C317" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D317" s="1" t="s">
-        <v>675</v>
-      </c>
       <c r="E317" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F317" s="1" t="s">
         <v>23</v>
@@ -9014,10 +9020,10 @@
         <v>3</v>
       </c>
       <c r="D318" s="1" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="E318" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F318" s="1" t="s">
         <v>23</v>
@@ -9034,13 +9040,13 @@
         <v>3</v>
       </c>
       <c r="D319" s="1" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="E319" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F319" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="320" spans="1:6" x14ac:dyDescent="0.25">
@@ -9054,10 +9060,10 @@
         <v>3</v>
       </c>
       <c r="D320" s="1" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="E320" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F320" s="1" t="s">
         <v>12</v>
@@ -9074,10 +9080,10 @@
         <v>3</v>
       </c>
       <c r="D321" s="1" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="E321" s="1" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F321" s="1" t="s">
         <v>12</v>
@@ -9094,10 +9100,10 @@
         <v>3</v>
       </c>
       <c r="D322" s="1" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="E322" s="1" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="F322" s="1" t="s">
         <v>12</v>
@@ -9114,10 +9120,10 @@
         <v>3</v>
       </c>
       <c r="D323" s="1" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="E323" s="1" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F323" s="1" t="s">
         <v>12</v>
@@ -9134,10 +9140,10 @@
         <v>3</v>
       </c>
       <c r="D324" s="1" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="E324" s="1" t="s">
-        <v>156</v>
+        <v>15</v>
       </c>
       <c r="F324" s="1" t="s">
         <v>12</v>
@@ -9154,10 +9160,10 @@
         <v>3</v>
       </c>
       <c r="D325" s="1" t="s">
-        <v>694</v>
+        <v>677</v>
       </c>
       <c r="E325" s="1" t="s">
-        <v>4</v>
+        <v>156</v>
       </c>
       <c r="F325" s="1" t="s">
         <v>12</v>
@@ -9165,19 +9171,19 @@
     </row>
     <row r="326" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A326" s="1" t="s">
+        <v>694</v>
+      </c>
+      <c r="B326" s="1" t="s">
         <v>695</v>
       </c>
-      <c r="B326" s="1" t="s">
+      <c r="C326" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D326" s="1" t="s">
         <v>696</v>
       </c>
-      <c r="C326" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D326" s="1" t="s">
-        <v>694</v>
-      </c>
       <c r="E326" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F326" s="1" t="s">
         <v>12</v>
@@ -9194,13 +9200,13 @@
         <v>3</v>
       </c>
       <c r="D327" s="1" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="E327" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F327" s="1" t="s">
-        <v>83</v>
+        <v>12</v>
       </c>
     </row>
     <row r="328" spans="1:6" x14ac:dyDescent="0.25">
@@ -9214,13 +9220,13 @@
         <v>3</v>
       </c>
       <c r="D328" s="1" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="E328" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F328" s="1" t="s">
-        <v>474</v>
+        <v>83</v>
       </c>
     </row>
     <row r="329" spans="1:6" x14ac:dyDescent="0.25">
@@ -9234,13 +9240,13 @@
         <v>3</v>
       </c>
       <c r="D329" s="1" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="E329" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F329" s="1" t="s">
-        <v>12</v>
+        <v>474</v>
       </c>
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.25">
@@ -9254,13 +9260,13 @@
         <v>3</v>
       </c>
       <c r="D330" s="1" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="E330" s="1" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F330" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="331" spans="1:6" x14ac:dyDescent="0.25">
@@ -9274,30 +9280,30 @@
         <v>3</v>
       </c>
       <c r="D331" s="1" t="s">
-        <v>707</v>
+        <v>696</v>
       </c>
       <c r="E331" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F331" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="332" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A332" s="1" t="s">
+        <v>707</v>
+      </c>
+      <c r="B332" s="1" t="s">
         <v>708</v>
       </c>
-      <c r="B332" s="1" t="s">
+      <c r="C332" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D332" s="1" t="s">
         <v>709</v>
       </c>
-      <c r="C332" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D332" s="1" t="s">
-        <v>707</v>
-      </c>
       <c r="E332" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F332" s="1" t="s">
         <v>12</v>
@@ -9314,13 +9320,13 @@
         <v>3</v>
       </c>
       <c r="D333" s="1" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="E333" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F333" s="1" t="s">
-        <v>83</v>
+        <v>12</v>
       </c>
     </row>
     <row r="334" spans="1:6" x14ac:dyDescent="0.25">
@@ -9334,13 +9340,13 @@
         <v>3</v>
       </c>
       <c r="D334" s="1" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="E334" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F334" s="1" t="s">
-        <v>23</v>
+        <v>83</v>
       </c>
     </row>
     <row r="335" spans="1:6" x14ac:dyDescent="0.25">
@@ -9354,13 +9360,13 @@
         <v>3</v>
       </c>
       <c r="D335" s="1" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="E335" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F335" s="1" t="s">
-        <v>83</v>
+        <v>23</v>
       </c>
     </row>
     <row r="336" spans="1:6" x14ac:dyDescent="0.25">
@@ -9374,13 +9380,13 @@
         <v>3</v>
       </c>
       <c r="D336" s="1" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="E336" s="1" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F336" s="1" t="s">
-        <v>12</v>
+        <v>83</v>
       </c>
     </row>
     <row r="337" spans="1:6" x14ac:dyDescent="0.25">
@@ -9394,30 +9400,30 @@
         <v>3</v>
       </c>
       <c r="D337" s="1" t="s">
-        <v>720</v>
+        <v>709</v>
       </c>
       <c r="E337" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F337" s="1" t="s">
-        <v>83</v>
+        <v>12</v>
       </c>
     </row>
     <row r="338" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A338" s="1" t="s">
+        <v>720</v>
+      </c>
+      <c r="B338" s="1" t="s">
         <v>721</v>
       </c>
-      <c r="B338" s="1" t="s">
+      <c r="C338" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D338" s="1" t="s">
         <v>722</v>
       </c>
-      <c r="C338" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D338" s="1" t="s">
-        <v>720</v>
-      </c>
       <c r="E338" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F338" s="1" t="s">
         <v>83</v>
@@ -9434,10 +9440,10 @@
         <v>3</v>
       </c>
       <c r="D339" s="1" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="E339" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F339" s="1" t="s">
         <v>83</v>
@@ -9454,10 +9460,10 @@
         <v>3</v>
       </c>
       <c r="D340" s="1" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="E340" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F340" s="1" t="s">
         <v>83</v>
@@ -9474,10 +9480,10 @@
         <v>3</v>
       </c>
       <c r="D341" s="1" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="E341" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F341" s="1" t="s">
         <v>83</v>
@@ -9494,10 +9500,10 @@
         <v>3</v>
       </c>
       <c r="D342" s="1" t="s">
-        <v>731</v>
+        <v>722</v>
       </c>
       <c r="E342" s="1" t="s">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="F342" s="1" t="s">
         <v>83</v>
@@ -9505,19 +9511,19 @@
     </row>
     <row r="343" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A343" s="1" t="s">
+        <v>731</v>
+      </c>
+      <c r="B343" s="1" t="s">
         <v>732</v>
       </c>
-      <c r="B343" s="1" t="s">
+      <c r="C343" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D343" s="1" t="s">
         <v>733</v>
       </c>
-      <c r="C343" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D343" s="1" t="s">
-        <v>731</v>
-      </c>
       <c r="E343" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F343" s="1" t="s">
         <v>83</v>
@@ -9534,10 +9540,10 @@
         <v>3</v>
       </c>
       <c r="D344" s="1" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="E344" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F344" s="1" t="s">
         <v>83</v>
@@ -9554,10 +9560,10 @@
         <v>3</v>
       </c>
       <c r="D345" s="1" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="E345" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F345" s="1" t="s">
         <v>83</v>
@@ -9574,13 +9580,13 @@
         <v>3</v>
       </c>
       <c r="D346" s="1" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="E346" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F346" s="1" t="s">
-        <v>12</v>
+        <v>83</v>
       </c>
     </row>
     <row r="347" spans="1:6" x14ac:dyDescent="0.25">
@@ -9594,33 +9600,33 @@
         <v>3</v>
       </c>
       <c r="D347" s="1" t="s">
-        <v>742</v>
+        <v>733</v>
       </c>
       <c r="E347" s="1" t="s">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="F347" s="1" t="s">
-        <v>743</v>
+        <v>12</v>
       </c>
     </row>
     <row r="348" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A348" s="1" t="s">
+        <v>742</v>
+      </c>
+      <c r="B348" s="1" t="s">
+        <v>743</v>
+      </c>
+      <c r="C348" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D348" s="1" t="s">
         <v>744</v>
       </c>
-      <c r="B348" s="1" t="s">
+      <c r="E348" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F348" s="1" t="s">
         <v>745</v>
-      </c>
-      <c r="C348" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D348" s="1" t="s">
-        <v>742</v>
-      </c>
-      <c r="E348" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F348" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="349" spans="1:6" x14ac:dyDescent="0.25">
@@ -9634,13 +9640,13 @@
         <v>3</v>
       </c>
       <c r="D349" s="1" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="E349" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F349" s="1" t="s">
-        <v>83</v>
+        <v>12</v>
       </c>
     </row>
     <row r="350" spans="1:6" x14ac:dyDescent="0.25">
@@ -9654,12 +9660,32 @@
         <v>3</v>
       </c>
       <c r="D350" s="1" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="E350" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F350" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="351" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A351" s="1" t="s">
+        <v>750</v>
+      </c>
+      <c r="B351" s="1" t="s">
+        <v>751</v>
+      </c>
+      <c r="C351" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D351" s="1" t="s">
+        <v>744</v>
+      </c>
+      <c r="E351" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F350" s="1" t="s">
+      <c r="F351" s="1" t="s">
         <v>83</v>
       </c>
     </row>

--- a/BFD05D.xlsx
+++ b/BFD05D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2106" uniqueCount="752">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2112" uniqueCount="754">
   <si>
     <t/>
   </si>
@@ -211,6 +211,12 @@
     <t>KOBE TP KNTKY SC 200</t>
   </si>
   <si>
+    <t>20144308</t>
+  </si>
+  <si>
+    <t>KBE T/B SRBGN GLD200</t>
+  </si>
+  <si>
     <t>20037353</t>
   </si>
   <si>
@@ -421,36 +427,48 @@
     <t>MASAKO SAPI 230GR</t>
   </si>
   <si>
+    <t>20133690</t>
+  </si>
+  <si>
+    <t>SEDAAP KALDU AYAM250</t>
+  </si>
+  <si>
+    <t>20143858</t>
+  </si>
+  <si>
+    <t>AJNMTO SJKU RNDNG60</t>
+  </si>
+  <si>
+    <t>10035899</t>
+  </si>
+  <si>
+    <t>A/MASAKO SAPI 94GR</t>
+  </si>
+  <si>
+    <t>20133691</t>
+  </si>
+  <si>
+    <t>SEDAAP KALDU SAPI250</t>
+  </si>
+  <si>
+    <t>20135316</t>
+  </si>
+  <si>
+    <t>LARISST BMB JMR 40G</t>
+  </si>
+  <si>
+    <t>20143857</t>
+  </si>
+  <si>
+    <t>AJNMTO SJIKU GULAI50</t>
+  </si>
+  <si>
     <t>20038549</t>
   </si>
   <si>
     <t>A/MASAKO AYAM 230GR</t>
   </si>
   <si>
-    <t>20143858</t>
-  </si>
-  <si>
-    <t>AJNMTO SJKU RNDNG60</t>
-  </si>
-  <si>
-    <t>10035899</t>
-  </si>
-  <si>
-    <t>A/MASAKO SAPI 94GR</t>
-  </si>
-  <si>
-    <t>20135316</t>
-  </si>
-  <si>
-    <t>LARISST BMB JMR 40G</t>
-  </si>
-  <si>
-    <t>20143857</t>
-  </si>
-  <si>
-    <t>AJNMTO SJIKU GULAI50</t>
-  </si>
-  <si>
     <t>20134250</t>
   </si>
   <si>
@@ -830,18 +848,6 @@
   </si>
   <si>
     <t>FINNA SMBL/T ULG 10S</t>
-  </si>
-  <si>
-    <t>20133690</t>
-  </si>
-  <si>
-    <t>SEDAAP KALDU AYAM250</t>
-  </si>
-  <si>
-    <t>20133691</t>
-  </si>
-  <si>
-    <t>SEDAAP KALDU SAPI250</t>
   </si>
   <si>
     <t>20129197</t>
@@ -2659,7 +2665,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F351"/>
+  <dimension ref="A1:F352"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -3226,7 +3232,7 @@
         <v>8</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -3246,7 +3252,7 @@
         <v>26</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -3266,7 +3272,7 @@
         <v>29</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -3300,10 +3306,10 @@
         <v>3</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>5</v>
@@ -3323,10 +3329,10 @@
         <v>11</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>41</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -3343,18 +3349,18 @@
         <v>11</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>80</v>
+        <v>41</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B35" s="1" t="s">
         <v>81</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>82</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>3</v>
@@ -3363,18 +3369,18 @@
         <v>11</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B36" s="1" t="s">
         <v>84</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>85</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>3</v>
@@ -3383,10 +3389,10 @@
         <v>11</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -3400,13 +3406,13 @@
         <v>3</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>5</v>
+        <v>82</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -3423,10 +3429,10 @@
         <v>34</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -3443,10 +3449,10 @@
         <v>34</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -3463,10 +3469,10 @@
         <v>34</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>12</v>
+        <v>41</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -3483,10 +3489,10 @@
         <v>34</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -3503,10 +3509,10 @@
         <v>34</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>83</v>
+        <v>23</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -3523,10 +3529,10 @@
         <v>34</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>12</v>
+        <v>85</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -3540,10 +3546,10 @@
         <v>3</v>
       </c>
       <c r="D44" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E44" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="E44" s="1" t="s">
-        <v>4</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>12</v>
@@ -3566,7 +3572,7 @@
         <v>4</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -3586,7 +3592,7 @@
         <v>4</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -3623,10 +3629,10 @@
         <v>15</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -3646,7 +3652,7 @@
         <v>18</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -3686,7 +3692,7 @@
         <v>18</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -3703,10 +3709,10 @@
         <v>15</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
@@ -3746,7 +3752,7 @@
         <v>8</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -3766,7 +3772,7 @@
         <v>8</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -3783,7 +3789,7 @@
         <v>15</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>12</v>
@@ -3863,7 +3869,7 @@
         <v>15</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>12</v>
@@ -3943,7 +3949,7 @@
         <v>15</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>12</v>
@@ -3966,7 +3972,7 @@
         <v>11</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>41</v>
+        <v>12</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
@@ -4003,10 +4009,10 @@
         <v>15</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>12</v>
+        <v>41</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
@@ -4023,10 +4029,10 @@
         <v>15</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
@@ -4043,10 +4049,10 @@
         <v>15</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
@@ -4063,10 +4069,10 @@
         <v>15</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
@@ -4080,73 +4086,73 @@
         <v>3</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>156</v>
+        <v>15</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B72" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="B72" s="1" t="s">
-        <v>158</v>
-      </c>
       <c r="C72" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>156</v>
+        <v>15</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="B73" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="B73" s="1" t="s">
-        <v>160</v>
-      </c>
       <c r="C73" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>156</v>
+        <v>15</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="B74" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="B74" s="1" t="s">
+      <c r="C74" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D74" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="C74" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D74" s="1" t="s">
-        <v>156</v>
-      </c>
       <c r="E74" s="1" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
@@ -4160,13 +4166,13 @@
         <v>3</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
@@ -4180,10 +4186,10 @@
         <v>3</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>12</v>
@@ -4200,13 +4206,13 @@
         <v>3</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
@@ -4220,13 +4226,13 @@
         <v>3</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>156</v>
+        <v>11</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
@@ -4240,10 +4246,10 @@
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>173</v>
+        <v>34</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>12</v>
@@ -4251,19 +4257,19 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B80" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="B80" s="1" t="s">
-        <v>175</v>
-      </c>
       <c r="C80" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>176</v>
+        <v>15</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>12</v>
@@ -4271,79 +4277,79 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>179</v>
+        <v>162</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>5</v>
@@ -4351,39 +4357,39 @@
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>4</v>
+        <v>188</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="E86" s="1" t="s">
         <v>191</v>
-      </c>
-      <c r="B86" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="C86" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D86" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="E86" s="1" t="s">
-        <v>18</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>23</v>
@@ -4391,22 +4397,22 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="B87" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="B87" s="1" t="s">
+      <c r="C87" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="E87" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="C87" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D87" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="E87" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="F87" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
@@ -4420,10 +4426,10 @@
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>23</v>
@@ -4440,13 +4446,13 @@
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
@@ -4460,13 +4466,13 @@
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
@@ -4480,13 +4486,13 @@
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
@@ -4500,10 +4506,10 @@
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>5</v>
@@ -4520,13 +4526,13 @@
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>156</v>
+        <v>11</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
@@ -4540,13 +4546,13 @@
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>173</v>
+        <v>34</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
@@ -4560,10 +4566,10 @@
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>176</v>
+        <v>15</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>5</v>
@@ -4580,13 +4586,13 @@
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>18</v>
+        <v>162</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
@@ -4600,13 +4606,13 @@
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>8</v>
+        <v>179</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
@@ -4620,10 +4626,10 @@
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>26</v>
+        <v>182</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>5</v>
@@ -4640,10 +4646,10 @@
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>5</v>
@@ -4660,13 +4666,13 @@
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
@@ -4680,13 +4686,13 @@
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
@@ -4700,13 +4706,13 @@
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
@@ -4720,10 +4726,10 @@
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>156</v>
+        <v>11</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>23</v>
@@ -4740,10 +4746,10 @@
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>173</v>
+        <v>34</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>23</v>
@@ -4760,13 +4766,13 @@
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>176</v>
+        <v>15</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
@@ -4780,13 +4786,13 @@
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>179</v>
+        <v>162</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
@@ -4800,13 +4806,13 @@
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
@@ -4820,13 +4826,13 @@
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
@@ -4840,13 +4846,13 @@
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
@@ -4860,50 +4866,50 @@
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>241</v>
+        <v>188</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="B111" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="B111" s="1" t="s">
-        <v>243</v>
-      </c>
       <c r="C111" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>244</v>
+        <v>191</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>4</v>
+        <v>194</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>5</v>
@@ -4911,39 +4917,39 @@
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D113" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="E113" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="B113" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="C113" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D113" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="E113" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="F113" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="B114" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="B114" s="1" t="s">
+      <c r="C114" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D114" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="E114" s="1" t="s">
         <v>250</v>
-      </c>
-      <c r="C114" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D114" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="E114" s="1" t="s">
-        <v>8</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>23</v>
@@ -4960,13 +4966,13 @@
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
@@ -4980,13 +4986,13 @@
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
@@ -5000,10 +5006,10 @@
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>23</v>
@@ -5020,10 +5026,10 @@
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>23</v>
@@ -5040,13 +5046,13 @@
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
@@ -5060,10 +5066,10 @@
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>156</v>
+        <v>11</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>23</v>
@@ -5080,13 +5086,13 @@
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
@@ -5100,10 +5106,10 @@
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>12</v>
@@ -5120,13 +5126,13 @@
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>8</v>
+        <v>162</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
@@ -5140,13 +5146,13 @@
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
@@ -5160,10 +5166,10 @@
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>12</v>
@@ -5180,10 +5186,10 @@
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>12</v>
@@ -5200,13 +5206,13 @@
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
@@ -5220,10 +5226,10 @@
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>12</v>
@@ -5240,10 +5246,10 @@
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>156</v>
+        <v>11</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>12</v>
@@ -5260,10 +5266,10 @@
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>173</v>
+        <v>34</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>12</v>
@@ -5280,10 +5286,10 @@
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>12</v>
@@ -5300,10 +5306,10 @@
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>12</v>
@@ -5320,10 +5326,10 @@
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>12</v>
@@ -5340,13 +5346,13 @@
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
@@ -5360,13 +5366,13 @@
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
@@ -5380,10 +5386,10 @@
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>12</v>
@@ -5400,10 +5406,10 @@
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>12</v>
@@ -5420,13 +5426,13 @@
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
@@ -5440,10 +5446,10 @@
         <v>3</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>156</v>
+        <v>15</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>23</v>
@@ -5460,13 +5466,13 @@
         <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>176</v>
+        <v>162</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
@@ -5480,10 +5486,10 @@
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="F141" s="1" t="s">
         <v>41</v>
@@ -5500,10 +5506,10 @@
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E142" s="1" t="s">
         <v>185</v>
-      </c>
-      <c r="E142" s="1" t="s">
-        <v>182</v>
       </c>
       <c r="F142" s="1" t="s">
         <v>41</v>
@@ -5520,10 +5526,10 @@
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>41</v>
@@ -5540,10 +5546,10 @@
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>41</v>
@@ -5560,13 +5566,13 @@
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>4</v>
+        <v>194</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
@@ -5580,7 +5586,7 @@
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="E146" s="1" t="s">
         <v>4</v>
@@ -5600,7 +5606,7 @@
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="E147" s="1" t="s">
         <v>4</v>
@@ -5620,7 +5626,7 @@
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="E148" s="1" t="s">
         <v>4</v>
@@ -5640,10 +5646,10 @@
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F149" s="1" t="s">
         <v>23</v>
@@ -5660,7 +5666,7 @@
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="E150" s="1" t="s">
         <v>18</v>
@@ -5680,7 +5686,7 @@
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="E151" s="1" t="s">
         <v>18</v>
@@ -5700,13 +5706,13 @@
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="E152" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
@@ -5720,13 +5726,13 @@
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
@@ -5740,7 +5746,7 @@
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="E154" s="1" t="s">
         <v>8</v>
@@ -5760,7 +5766,7 @@
         <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="E155" s="1" t="s">
         <v>8</v>
@@ -5780,7 +5786,7 @@
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="E156" s="1" t="s">
         <v>8</v>
@@ -5800,10 +5806,10 @@
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>23</v>
@@ -5820,7 +5826,7 @@
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="E158" s="1" t="s">
         <v>26</v>
@@ -5840,7 +5846,7 @@
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="E159" s="1" t="s">
         <v>26</v>
@@ -5860,13 +5866,13 @@
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="E160" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
@@ -5880,13 +5886,13 @@
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
@@ -5900,7 +5906,7 @@
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="E162" s="1" t="s">
         <v>29</v>
@@ -5920,7 +5926,7 @@
         <v>3</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="E163" s="1" t="s">
         <v>29</v>
@@ -5940,7 +5946,7 @@
         <v>3</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="E164" s="1" t="s">
         <v>29</v>
@@ -5960,10 +5966,10 @@
         <v>3</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F165" s="1" t="s">
         <v>23</v>
@@ -5980,7 +5986,7 @@
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="E166" s="1" t="s">
         <v>11</v>
@@ -6000,7 +6006,7 @@
         <v>3</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="E167" s="1" t="s">
         <v>11</v>
@@ -6020,7 +6026,7 @@
         <v>3</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="E168" s="1" t="s">
         <v>11</v>
@@ -6040,13 +6046,13 @@
         <v>3</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
@@ -6060,7 +6066,7 @@
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="E170" s="1" t="s">
         <v>34</v>
@@ -6080,7 +6086,7 @@
         <v>3</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="E171" s="1" t="s">
         <v>34</v>
@@ -6100,7 +6106,7 @@
         <v>3</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="E172" s="1" t="s">
         <v>34</v>
@@ -6120,33 +6126,33 @@
         <v>3</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>369</v>
+        <v>12</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="B174" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="B174" s="1" t="s">
-        <v>371</v>
-      </c>
       <c r="C174" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="E174" s="1" t="s">
         <v>15</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>12</v>
+        <v>371</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
@@ -6160,13 +6166,13 @@
         <v>3</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>241</v>
+        <v>194</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
@@ -6180,13 +6186,13 @@
         <v>3</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
@@ -6200,13 +6206,13 @@
         <v>3</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
@@ -6220,33 +6226,33 @@
         <v>3</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>380</v>
+        <v>5</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="B179" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="B179" s="1" t="s">
+      <c r="C179" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D179" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="E179" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F179" s="1" t="s">
         <v>382</v>
-      </c>
-      <c r="C179" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D179" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="E179" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F179" s="1" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
@@ -6260,13 +6266,13 @@
         <v>3</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>12</v>
+        <v>85</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
@@ -6280,13 +6286,13 @@
         <v>3</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
@@ -6300,13 +6306,13 @@
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="F182" s="1" t="s">
-        <v>369</v>
+        <v>23</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
@@ -6320,13 +6326,13 @@
         <v>3</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
@@ -6340,13 +6346,13 @@
         <v>3</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>5</v>
+        <v>371</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
@@ -6360,10 +6366,10 @@
         <v>3</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F185" s="1" t="s">
         <v>5</v>
@@ -6380,10 +6386,10 @@
         <v>3</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F186" s="1" t="s">
         <v>5</v>
@@ -6400,13 +6406,13 @@
         <v>3</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
@@ -6420,10 +6426,10 @@
         <v>3</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="F188" s="1" t="s">
         <v>12</v>
@@ -6440,10 +6446,10 @@
         <v>3</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F189" s="1" t="s">
         <v>12</v>
@@ -6460,10 +6466,10 @@
         <v>3</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>405</v>
+        <v>250</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F190" s="1" t="s">
         <v>12</v>
@@ -6471,19 +6477,19 @@
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="B191" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="B191" s="1" t="s">
+      <c r="C191" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D191" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="C191" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D191" s="1" t="s">
-        <v>405</v>
-      </c>
       <c r="E191" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F191" s="1" t="s">
         <v>12</v>
@@ -6500,13 +6506,13 @@
         <v>3</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F192" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
@@ -6520,10 +6526,10 @@
         <v>3</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F193" s="1" t="s">
         <v>23</v>
@@ -6540,13 +6546,13 @@
         <v>3</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F194" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
@@ -6560,13 +6566,13 @@
         <v>3</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F195" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
@@ -6580,13 +6586,13 @@
         <v>3</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="F196" s="1" t="s">
-        <v>369</v>
+        <v>23</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
@@ -6600,13 +6606,13 @@
         <v>3</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F197" s="1" t="s">
-        <v>5</v>
+        <v>371</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
@@ -6620,13 +6626,13 @@
         <v>3</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>156</v>
+        <v>15</v>
       </c>
       <c r="F198" s="1" t="s">
-        <v>369</v>
+        <v>5</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
@@ -6640,13 +6646,13 @@
         <v>3</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="F199" s="1" t="s">
-        <v>5</v>
+        <v>371</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
@@ -6660,10 +6666,10 @@
         <v>3</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>426</v>
+        <v>407</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>4</v>
+        <v>179</v>
       </c>
       <c r="F200" s="1" t="s">
         <v>5</v>
@@ -6671,19 +6677,19 @@
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="B201" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="B201" s="1" t="s">
+      <c r="C201" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D201" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="C201" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D201" s="1" t="s">
-        <v>426</v>
-      </c>
       <c r="E201" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F201" s="1" t="s">
         <v>5</v>
@@ -6700,10 +6706,10 @@
         <v>3</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F202" s="1" t="s">
         <v>5</v>
@@ -6720,10 +6726,10 @@
         <v>3</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F203" s="1" t="s">
         <v>5</v>
@@ -6740,10 +6746,10 @@
         <v>3</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F204" s="1" t="s">
         <v>5</v>
@@ -6760,13 +6766,13 @@
         <v>3</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F205" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
@@ -6780,13 +6786,13 @@
         <v>3</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="F206" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
@@ -6800,10 +6806,10 @@
         <v>3</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F207" s="1" t="s">
         <v>12</v>
@@ -6820,10 +6826,10 @@
         <v>3</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>156</v>
+        <v>15</v>
       </c>
       <c r="F208" s="1" t="s">
         <v>12</v>
@@ -6840,10 +6846,10 @@
         <v>3</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="F209" s="1" t="s">
         <v>12</v>
@@ -6860,13 +6866,13 @@
         <v>3</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="F210" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
@@ -6880,33 +6886,33 @@
         <v>3</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>449</v>
+        <v>428</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>4</v>
+        <v>182</v>
       </c>
       <c r="F211" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="B212" s="1" t="s">
         <v>450</v>
       </c>
-      <c r="B212" s="1" t="s">
+      <c r="C212" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D212" s="1" t="s">
         <v>451</v>
       </c>
-      <c r="C212" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D212" s="1" t="s">
-        <v>449</v>
-      </c>
       <c r="E212" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F212" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
@@ -6920,13 +6926,13 @@
         <v>3</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F213" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
@@ -6940,13 +6946,13 @@
         <v>3</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F214" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
@@ -6960,10 +6966,10 @@
         <v>3</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F215" s="1" t="s">
         <v>5</v>
@@ -6980,13 +6986,13 @@
         <v>3</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F216" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
@@ -7000,10 +7006,10 @@
         <v>3</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="F217" s="1" t="s">
         <v>12</v>
@@ -7020,33 +7026,33 @@
         <v>3</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="E218" s="1" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F218" s="1" t="s">
-        <v>464</v>
+        <v>12</v>
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="B219" s="1" t="s">
         <v>465</v>
       </c>
-      <c r="B219" s="1" t="s">
+      <c r="C219" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D219" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="E219" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F219" s="1" t="s">
         <v>466</v>
-      </c>
-      <c r="C219" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D219" s="1" t="s">
-        <v>449</v>
-      </c>
-      <c r="E219" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="F219" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
@@ -7060,13 +7066,13 @@
         <v>3</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="E220" s="1" t="s">
-        <v>176</v>
+        <v>162</v>
       </c>
       <c r="F220" s="1" t="s">
-        <v>83</v>
+        <v>5</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
@@ -7080,13 +7086,13 @@
         <v>3</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="E221" s="1" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="F221" s="1" t="s">
-        <v>12</v>
+        <v>85</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
@@ -7100,33 +7106,33 @@
         <v>3</v>
       </c>
       <c r="D222" s="1" t="s">
-        <v>473</v>
+        <v>451</v>
       </c>
       <c r="E222" s="1" t="s">
-        <v>4</v>
+        <v>185</v>
       </c>
       <c r="F222" s="1" t="s">
-        <v>474</v>
+        <v>12</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="B223" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="C223" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D223" s="1" t="s">
         <v>475</v>
       </c>
-      <c r="B223" s="1" t="s">
+      <c r="E223" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F223" s="1" t="s">
         <v>476</v>
-      </c>
-      <c r="C223" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D223" s="1" t="s">
-        <v>473</v>
-      </c>
-      <c r="E223" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F223" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
@@ -7140,10 +7146,10 @@
         <v>3</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="E224" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F224" s="1" t="s">
         <v>23</v>
@@ -7160,13 +7166,13 @@
         <v>3</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="E225" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F225" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
@@ -7180,13 +7186,13 @@
         <v>3</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="E226" s="1" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F226" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
@@ -7200,13 +7206,13 @@
         <v>3</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="E227" s="1" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="F227" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
@@ -7220,10 +7226,10 @@
         <v>3</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="E228" s="1" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F228" s="1" t="s">
         <v>5</v>
@@ -7240,13 +7246,13 @@
         <v>3</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="E229" s="1" t="s">
-        <v>156</v>
+        <v>15</v>
       </c>
       <c r="F229" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
@@ -7260,10 +7266,10 @@
         <v>3</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="E230" s="1" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="F230" s="1" t="s">
         <v>23</v>
@@ -7280,10 +7286,10 @@
         <v>3</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="E231" s="1" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="F231" s="1" t="s">
         <v>23</v>
@@ -7300,10 +7306,10 @@
         <v>3</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="E232" s="1" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="F232" s="1" t="s">
         <v>23</v>
@@ -7320,10 +7326,10 @@
         <v>3</v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="E233" s="1" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="F233" s="1" t="s">
         <v>23</v>
@@ -7340,33 +7346,33 @@
         <v>3</v>
       </c>
       <c r="D234" s="1" t="s">
-        <v>499</v>
+        <v>475</v>
       </c>
       <c r="E234" s="1" t="s">
-        <v>4</v>
+        <v>188</v>
       </c>
       <c r="F234" s="1" t="s">
-        <v>500</v>
+        <v>23</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A235" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="B235" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="C235" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D235" s="1" t="s">
         <v>501</v>
-      </c>
-      <c r="B235" s="1" t="s">
-        <v>502</v>
-      </c>
-      <c r="C235" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D235" s="1" t="s">
-        <v>499</v>
       </c>
       <c r="E235" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F235" s="1" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.25">
@@ -7380,13 +7386,13 @@
         <v>3</v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="E236" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F236" s="1" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.25">
@@ -7400,13 +7406,13 @@
         <v>3</v>
       </c>
       <c r="D237" s="1" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="E237" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F237" s="1" t="s">
-        <v>83</v>
+        <v>502</v>
       </c>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.25">
@@ -7420,13 +7426,13 @@
         <v>3</v>
       </c>
       <c r="D238" s="1" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="E238" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F238" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.25">
@@ -7440,13 +7446,13 @@
         <v>3</v>
       </c>
       <c r="D239" s="1" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="E239" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F239" s="1" t="s">
-        <v>500</v>
+        <v>85</v>
       </c>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.25">
@@ -7460,13 +7466,13 @@
         <v>3</v>
       </c>
       <c r="D240" s="1" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="E240" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F240" s="1" t="s">
-        <v>83</v>
+        <v>502</v>
       </c>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.25">
@@ -7480,13 +7486,13 @@
         <v>3</v>
       </c>
       <c r="D241" s="1" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="E241" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F241" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.25">
@@ -7500,13 +7506,13 @@
         <v>3</v>
       </c>
       <c r="D242" s="1" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="E242" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F242" s="1" t="s">
-        <v>5</v>
+        <v>85</v>
       </c>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.25">
@@ -7520,10 +7526,10 @@
         <v>3</v>
       </c>
       <c r="D243" s="1" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="E243" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F243" s="1" t="s">
         <v>5</v>
@@ -7540,7 +7546,7 @@
         <v>3</v>
       </c>
       <c r="D244" s="1" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="E244" s="1" t="s">
         <v>26</v>
@@ -7560,7 +7566,7 @@
         <v>3</v>
       </c>
       <c r="D245" s="1" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="E245" s="1" t="s">
         <v>26</v>
@@ -7580,10 +7586,10 @@
         <v>3</v>
       </c>
       <c r="D246" s="1" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="E246" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F246" s="1" t="s">
         <v>5</v>
@@ -7600,7 +7606,7 @@
         <v>3</v>
       </c>
       <c r="D247" s="1" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="E247" s="1" t="s">
         <v>29</v>
@@ -7620,7 +7626,7 @@
         <v>3</v>
       </c>
       <c r="D248" s="1" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="E248" s="1" t="s">
         <v>29</v>
@@ -7640,10 +7646,10 @@
         <v>3</v>
       </c>
       <c r="D249" s="1" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="E249" s="1" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F249" s="1" t="s">
         <v>5</v>
@@ -7660,7 +7666,7 @@
         <v>3</v>
       </c>
       <c r="D250" s="1" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="E250" s="1" t="s">
         <v>11</v>
@@ -7680,7 +7686,7 @@
         <v>3</v>
       </c>
       <c r="D251" s="1" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="E251" s="1" t="s">
         <v>11</v>
@@ -7700,10 +7706,10 @@
         <v>3</v>
       </c>
       <c r="D252" s="1" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="E252" s="1" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="F252" s="1" t="s">
         <v>5</v>
@@ -7720,7 +7726,7 @@
         <v>3</v>
       </c>
       <c r="D253" s="1" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="E253" s="1" t="s">
         <v>34</v>
@@ -7740,7 +7746,7 @@
         <v>3</v>
       </c>
       <c r="D254" s="1" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="E254" s="1" t="s">
         <v>34</v>
@@ -7760,10 +7766,10 @@
         <v>3</v>
       </c>
       <c r="D255" s="1" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="E255" s="1" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F255" s="1" t="s">
         <v>5</v>
@@ -7780,10 +7786,10 @@
         <v>3</v>
       </c>
       <c r="D256" s="1" t="s">
-        <v>545</v>
+        <v>501</v>
       </c>
       <c r="E256" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F256" s="1" t="s">
         <v>5</v>
@@ -7791,19 +7797,19 @@
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A257" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="B257" s="1" t="s">
         <v>546</v>
       </c>
-      <c r="B257" s="1" t="s">
+      <c r="C257" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D257" s="1" t="s">
         <v>547</v>
       </c>
-      <c r="C257" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D257" s="1" t="s">
-        <v>545</v>
-      </c>
       <c r="E257" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F257" s="1" t="s">
         <v>5</v>
@@ -7820,10 +7826,10 @@
         <v>3</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="E258" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F258" s="1" t="s">
         <v>5</v>
@@ -7840,13 +7846,13 @@
         <v>3</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="E259" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F259" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.25">
@@ -7860,13 +7866,13 @@
         <v>3</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="E260" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F260" s="1" t="s">
-        <v>83</v>
+        <v>23</v>
       </c>
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.25">
@@ -7880,30 +7886,30 @@
         <v>3</v>
       </c>
       <c r="D261" s="1" t="s">
-        <v>556</v>
+        <v>547</v>
       </c>
       <c r="E261" s="1" t="s">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="F261" s="1" t="s">
-        <v>5</v>
+        <v>85</v>
       </c>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A262" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="B262" s="1" t="s">
         <v>557</v>
       </c>
-      <c r="B262" s="1" t="s">
+      <c r="C262" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D262" s="1" t="s">
         <v>558</v>
       </c>
-      <c r="C262" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D262" s="1" t="s">
-        <v>556</v>
-      </c>
       <c r="E262" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F262" s="1" t="s">
         <v>5</v>
@@ -7920,10 +7926,10 @@
         <v>3</v>
       </c>
       <c r="D263" s="1" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="E263" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F263" s="1" t="s">
         <v>5</v>
@@ -7940,13 +7946,13 @@
         <v>3</v>
       </c>
       <c r="D264" s="1" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="E264" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F264" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.25">
@@ -7960,10 +7966,10 @@
         <v>3</v>
       </c>
       <c r="D265" s="1" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="E265" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F265" s="1" t="s">
         <v>23</v>
@@ -7980,13 +7986,13 @@
         <v>3</v>
       </c>
       <c r="D266" s="1" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="E266" s="1" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F266" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.25">
@@ -8000,13 +8006,13 @@
         <v>3</v>
       </c>
       <c r="D267" s="1" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="E267" s="1" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="F267" s="1" t="s">
-        <v>83</v>
+        <v>5</v>
       </c>
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.25">
@@ -8020,30 +8026,30 @@
         <v>3</v>
       </c>
       <c r="D268" s="1" t="s">
-        <v>571</v>
+        <v>558</v>
       </c>
       <c r="E268" s="1" t="s">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="F268" s="1" t="s">
-        <v>5</v>
+        <v>85</v>
       </c>
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A269" s="1" t="s">
+        <v>571</v>
+      </c>
+      <c r="B269" s="1" t="s">
         <v>572</v>
       </c>
-      <c r="B269" s="1" t="s">
+      <c r="C269" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D269" s="1" t="s">
         <v>573</v>
       </c>
-      <c r="C269" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D269" s="1" t="s">
-        <v>571</v>
-      </c>
       <c r="E269" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F269" s="1" t="s">
         <v>5</v>
@@ -8060,10 +8066,10 @@
         <v>3</v>
       </c>
       <c r="D270" s="1" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="E270" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F270" s="1" t="s">
         <v>5</v>
@@ -8080,13 +8086,13 @@
         <v>3</v>
       </c>
       <c r="D271" s="1" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="E271" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F271" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.25">
@@ -8100,10 +8106,10 @@
         <v>3</v>
       </c>
       <c r="D272" s="1" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="E272" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F272" s="1" t="s">
         <v>23</v>
@@ -8120,13 +8126,13 @@
         <v>3</v>
       </c>
       <c r="D273" s="1" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="E273" s="1" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F273" s="1" t="s">
-        <v>83</v>
+        <v>23</v>
       </c>
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.25">
@@ -8140,33 +8146,33 @@
         <v>3</v>
       </c>
       <c r="D274" s="1" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="E274" s="1" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="F274" s="1" t="s">
-        <v>584</v>
+        <v>85</v>
       </c>
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A275" s="1" t="s">
+        <v>584</v>
+      </c>
+      <c r="B275" s="1" t="s">
         <v>585</v>
       </c>
-      <c r="B275" s="1" t="s">
+      <c r="C275" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D275" s="1" t="s">
+        <v>573</v>
+      </c>
+      <c r="E275" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F275" s="1" t="s">
         <v>586</v>
-      </c>
-      <c r="C275" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D275" s="1" t="s">
-        <v>571</v>
-      </c>
-      <c r="E275" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="F275" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.25">
@@ -8180,13 +8186,13 @@
         <v>3</v>
       </c>
       <c r="D276" s="1" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="E276" s="1" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="F276" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.25">
@@ -8200,13 +8206,13 @@
         <v>3</v>
       </c>
       <c r="D277" s="1" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="E277" s="1" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="F277" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.25">
@@ -8220,33 +8226,33 @@
         <v>3</v>
       </c>
       <c r="D278" s="1" t="s">
-        <v>593</v>
+        <v>573</v>
       </c>
       <c r="E278" s="1" t="s">
-        <v>4</v>
+        <v>182</v>
       </c>
       <c r="F278" s="1" t="s">
-        <v>83</v>
+        <v>12</v>
       </c>
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A279" s="1" t="s">
+        <v>593</v>
+      </c>
+      <c r="B279" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="B279" s="1" t="s">
+      <c r="C279" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D279" s="1" t="s">
         <v>595</v>
       </c>
-      <c r="C279" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D279" s="1" t="s">
-        <v>593</v>
-      </c>
       <c r="E279" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F279" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.25">
@@ -8260,13 +8266,13 @@
         <v>3</v>
       </c>
       <c r="D280" s="1" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="E280" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F280" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.25">
@@ -8280,13 +8286,13 @@
         <v>3</v>
       </c>
       <c r="D281" s="1" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="E281" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F281" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.25">
@@ -8300,33 +8306,33 @@
         <v>3</v>
       </c>
       <c r="D282" s="1" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="E282" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F282" s="1" t="s">
-        <v>602</v>
+        <v>85</v>
       </c>
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A283" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="B283" s="1" t="s">
         <v>603</v>
       </c>
-      <c r="B283" s="1" t="s">
+      <c r="C283" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D283" s="1" t="s">
+        <v>595</v>
+      </c>
+      <c r="E283" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F283" s="1" t="s">
         <v>604</v>
-      </c>
-      <c r="C283" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D283" s="1" t="s">
-        <v>593</v>
-      </c>
-      <c r="E283" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F283" s="1" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.25">
@@ -8340,13 +8346,13 @@
         <v>3</v>
       </c>
       <c r="D284" s="1" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="E284" s="1" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="F284" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.25">
@@ -8360,13 +8366,13 @@
         <v>3</v>
       </c>
       <c r="D285" s="1" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="E285" s="1" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F285" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.25">
@@ -8380,30 +8386,30 @@
         <v>3</v>
       </c>
       <c r="D286" s="1" t="s">
-        <v>611</v>
+        <v>595</v>
       </c>
       <c r="E286" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F286" s="1" t="s">
-        <v>12</v>
+        <v>85</v>
       </c>
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A287" s="1" t="s">
+        <v>611</v>
+      </c>
+      <c r="B287" s="1" t="s">
         <v>612</v>
       </c>
-      <c r="B287" s="1" t="s">
+      <c r="C287" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D287" s="1" t="s">
         <v>613</v>
       </c>
-      <c r="C287" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D287" s="1" t="s">
-        <v>611</v>
-      </c>
       <c r="E287" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F287" s="1" t="s">
         <v>12</v>
@@ -8420,10 +8426,10 @@
         <v>3</v>
       </c>
       <c r="D288" s="1" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="E288" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F288" s="1" t="s">
         <v>12</v>
@@ -8440,10 +8446,10 @@
         <v>3</v>
       </c>
       <c r="D289" s="1" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="E289" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F289" s="1" t="s">
         <v>12</v>
@@ -8460,13 +8466,13 @@
         <v>3</v>
       </c>
       <c r="D290" s="1" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="E290" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F290" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.25">
@@ -8480,10 +8486,10 @@
         <v>3</v>
       </c>
       <c r="D291" s="1" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="E291" s="1" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F291" s="1" t="s">
         <v>23</v>
@@ -8500,10 +8506,10 @@
         <v>3</v>
       </c>
       <c r="D292" s="1" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="E292" s="1" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="F292" s="1" t="s">
         <v>23</v>
@@ -8520,13 +8526,13 @@
         <v>3</v>
       </c>
       <c r="D293" s="1" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="E293" s="1" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F293" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.25">
@@ -8540,33 +8546,33 @@
         <v>3</v>
       </c>
       <c r="D294" s="1" t="s">
-        <v>628</v>
+        <v>613</v>
       </c>
       <c r="E294" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F294" s="1" t="s">
-        <v>629</v>
+        <v>12</v>
       </c>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A295" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="B295" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="C295" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D295" s="1" t="s">
         <v>630</v>
       </c>
-      <c r="B295" s="1" t="s">
+      <c r="E295" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F295" s="1" t="s">
         <v>631</v>
-      </c>
-      <c r="C295" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D295" s="1" t="s">
-        <v>628</v>
-      </c>
-      <c r="E295" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F295" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.25">
@@ -8580,10 +8586,10 @@
         <v>3</v>
       </c>
       <c r="D296" s="1" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="E296" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F296" s="1" t="s">
         <v>12</v>
@@ -8600,10 +8606,10 @@
         <v>3</v>
       </c>
       <c r="D297" s="1" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="E297" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F297" s="1" t="s">
         <v>12</v>
@@ -8620,10 +8626,10 @@
         <v>3</v>
       </c>
       <c r="D298" s="1" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="E298" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F298" s="1" t="s">
         <v>12</v>
@@ -8640,13 +8646,13 @@
         <v>3</v>
       </c>
       <c r="D299" s="1" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="E299" s="1" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F299" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.25">
@@ -8660,13 +8666,13 @@
         <v>3</v>
       </c>
       <c r="D300" s="1" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="E300" s="1" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="F300" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.25">
@@ -8680,10 +8686,10 @@
         <v>3</v>
       </c>
       <c r="D301" s="1" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="E301" s="1" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F301" s="1" t="s">
         <v>12</v>
@@ -8700,10 +8706,10 @@
         <v>3</v>
       </c>
       <c r="D302" s="1" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="E302" s="1" t="s">
-        <v>156</v>
+        <v>15</v>
       </c>
       <c r="F302" s="1" t="s">
         <v>12</v>
@@ -8720,10 +8726,10 @@
         <v>3</v>
       </c>
       <c r="D303" s="1" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="E303" s="1" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="F303" s="1" t="s">
         <v>12</v>
@@ -8740,10 +8746,10 @@
         <v>3</v>
       </c>
       <c r="D304" s="1" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="E304" s="1" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="F304" s="1" t="s">
         <v>12</v>
@@ -8760,13 +8766,13 @@
         <v>3</v>
       </c>
       <c r="D305" s="1" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="E305" s="1" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="F305" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.25">
@@ -8780,13 +8786,13 @@
         <v>3</v>
       </c>
       <c r="D306" s="1" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="E306" s="1" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="F306" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.25">
@@ -8800,13 +8806,13 @@
         <v>3</v>
       </c>
       <c r="D307" s="1" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="E307" s="1" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="F307" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="308" spans="1:6" x14ac:dyDescent="0.25">
@@ -8820,13 +8826,13 @@
         <v>3</v>
       </c>
       <c r="D308" s="1" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="E308" s="1" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="F308" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="309" spans="1:6" x14ac:dyDescent="0.25">
@@ -8840,10 +8846,10 @@
         <v>3</v>
       </c>
       <c r="D309" s="1" t="s">
-        <v>660</v>
+        <v>630</v>
       </c>
       <c r="E309" s="1" t="s">
-        <v>4</v>
+        <v>194</v>
       </c>
       <c r="F309" s="1" t="s">
         <v>12</v>
@@ -8851,22 +8857,22 @@
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A310" s="1" t="s">
+        <v>660</v>
+      </c>
+      <c r="B310" s="1" t="s">
         <v>661</v>
       </c>
-      <c r="B310" s="1" t="s">
+      <c r="C310" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D310" s="1" t="s">
         <v>662</v>
       </c>
-      <c r="C310" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D310" s="1" t="s">
-        <v>660</v>
-      </c>
       <c r="E310" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F310" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.25">
@@ -8880,13 +8886,13 @@
         <v>3</v>
       </c>
       <c r="D311" s="1" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="E311" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F311" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="312" spans="1:6" x14ac:dyDescent="0.25">
@@ -8900,10 +8906,10 @@
         <v>3</v>
       </c>
       <c r="D312" s="1" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="E312" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F312" s="1" t="s">
         <v>12</v>
@@ -8920,10 +8926,10 @@
         <v>3</v>
       </c>
       <c r="D313" s="1" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="E313" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F313" s="1" t="s">
         <v>12</v>
@@ -8940,10 +8946,10 @@
         <v>3</v>
       </c>
       <c r="D314" s="1" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="E314" s="1" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F314" s="1" t="s">
         <v>12</v>
@@ -8960,10 +8966,10 @@
         <v>3</v>
       </c>
       <c r="D315" s="1" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="E315" s="1" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F315" s="1" t="s">
         <v>12</v>
@@ -8980,13 +8986,13 @@
         <v>3</v>
       </c>
       <c r="D316" s="1" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="E316" s="1" t="s">
-        <v>156</v>
+        <v>15</v>
       </c>
       <c r="F316" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="317" spans="1:6" x14ac:dyDescent="0.25">
@@ -9000,10 +9006,10 @@
         <v>3</v>
       </c>
       <c r="D317" s="1" t="s">
-        <v>677</v>
+        <v>662</v>
       </c>
       <c r="E317" s="1" t="s">
-        <v>4</v>
+        <v>162</v>
       </c>
       <c r="F317" s="1" t="s">
         <v>23</v>
@@ -9011,19 +9017,19 @@
     </row>
     <row r="318" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A318" s="1" t="s">
+        <v>677</v>
+      </c>
+      <c r="B318" s="1" t="s">
         <v>678</v>
       </c>
-      <c r="B318" s="1" t="s">
+      <c r="C318" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D318" s="1" t="s">
         <v>679</v>
       </c>
-      <c r="C318" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D318" s="1" t="s">
-        <v>677</v>
-      </c>
       <c r="E318" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F318" s="1" t="s">
         <v>23</v>
@@ -9040,10 +9046,10 @@
         <v>3</v>
       </c>
       <c r="D319" s="1" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="E319" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F319" s="1" t="s">
         <v>23</v>
@@ -9060,13 +9066,13 @@
         <v>3</v>
       </c>
       <c r="D320" s="1" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="E320" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F320" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="321" spans="1:6" x14ac:dyDescent="0.25">
@@ -9080,10 +9086,10 @@
         <v>3</v>
       </c>
       <c r="D321" s="1" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="E321" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F321" s="1" t="s">
         <v>12</v>
@@ -9100,10 +9106,10 @@
         <v>3</v>
       </c>
       <c r="D322" s="1" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="E322" s="1" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F322" s="1" t="s">
         <v>12</v>
@@ -9120,10 +9126,10 @@
         <v>3</v>
       </c>
       <c r="D323" s="1" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="E323" s="1" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="F323" s="1" t="s">
         <v>12</v>
@@ -9140,10 +9146,10 @@
         <v>3</v>
       </c>
       <c r="D324" s="1" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="E324" s="1" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F324" s="1" t="s">
         <v>12</v>
@@ -9160,10 +9166,10 @@
         <v>3</v>
       </c>
       <c r="D325" s="1" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="E325" s="1" t="s">
-        <v>156</v>
+        <v>15</v>
       </c>
       <c r="F325" s="1" t="s">
         <v>12</v>
@@ -9180,10 +9186,10 @@
         <v>3</v>
       </c>
       <c r="D326" s="1" t="s">
-        <v>696</v>
+        <v>679</v>
       </c>
       <c r="E326" s="1" t="s">
-        <v>4</v>
+        <v>162</v>
       </c>
       <c r="F326" s="1" t="s">
         <v>12</v>
@@ -9191,19 +9197,19 @@
     </row>
     <row r="327" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A327" s="1" t="s">
+        <v>696</v>
+      </c>
+      <c r="B327" s="1" t="s">
         <v>697</v>
       </c>
-      <c r="B327" s="1" t="s">
+      <c r="C327" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D327" s="1" t="s">
         <v>698</v>
       </c>
-      <c r="C327" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D327" s="1" t="s">
-        <v>696</v>
-      </c>
       <c r="E327" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F327" s="1" t="s">
         <v>12</v>
@@ -9220,13 +9226,13 @@
         <v>3</v>
       </c>
       <c r="D328" s="1" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="E328" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F328" s="1" t="s">
-        <v>83</v>
+        <v>12</v>
       </c>
     </row>
     <row r="329" spans="1:6" x14ac:dyDescent="0.25">
@@ -9240,13 +9246,13 @@
         <v>3</v>
       </c>
       <c r="D329" s="1" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="E329" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F329" s="1" t="s">
-        <v>474</v>
+        <v>85</v>
       </c>
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.25">
@@ -9260,13 +9266,13 @@
         <v>3</v>
       </c>
       <c r="D330" s="1" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="E330" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F330" s="1" t="s">
-        <v>12</v>
+        <v>476</v>
       </c>
     </row>
     <row r="331" spans="1:6" x14ac:dyDescent="0.25">
@@ -9280,13 +9286,13 @@
         <v>3</v>
       </c>
       <c r="D331" s="1" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="E331" s="1" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F331" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="332" spans="1:6" x14ac:dyDescent="0.25">
@@ -9300,30 +9306,30 @@
         <v>3</v>
       </c>
       <c r="D332" s="1" t="s">
-        <v>709</v>
+        <v>698</v>
       </c>
       <c r="E332" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F332" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="333" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A333" s="1" t="s">
+        <v>709</v>
+      </c>
+      <c r="B333" s="1" t="s">
         <v>710</v>
       </c>
-      <c r="B333" s="1" t="s">
+      <c r="C333" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D333" s="1" t="s">
         <v>711</v>
       </c>
-      <c r="C333" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D333" s="1" t="s">
-        <v>709</v>
-      </c>
       <c r="E333" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F333" s="1" t="s">
         <v>12</v>
@@ -9340,13 +9346,13 @@
         <v>3</v>
       </c>
       <c r="D334" s="1" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="E334" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F334" s="1" t="s">
-        <v>83</v>
+        <v>12</v>
       </c>
     </row>
     <row r="335" spans="1:6" x14ac:dyDescent="0.25">
@@ -9360,13 +9366,13 @@
         <v>3</v>
       </c>
       <c r="D335" s="1" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="E335" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F335" s="1" t="s">
-        <v>23</v>
+        <v>85</v>
       </c>
     </row>
     <row r="336" spans="1:6" x14ac:dyDescent="0.25">
@@ -9380,13 +9386,13 @@
         <v>3</v>
       </c>
       <c r="D336" s="1" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="E336" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F336" s="1" t="s">
-        <v>83</v>
+        <v>23</v>
       </c>
     </row>
     <row r="337" spans="1:6" x14ac:dyDescent="0.25">
@@ -9400,13 +9406,13 @@
         <v>3</v>
       </c>
       <c r="D337" s="1" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="E337" s="1" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F337" s="1" t="s">
-        <v>12</v>
+        <v>85</v>
       </c>
     </row>
     <row r="338" spans="1:6" x14ac:dyDescent="0.25">
@@ -9420,33 +9426,33 @@
         <v>3</v>
       </c>
       <c r="D338" s="1" t="s">
-        <v>722</v>
+        <v>711</v>
       </c>
       <c r="E338" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F338" s="1" t="s">
-        <v>83</v>
+        <v>12</v>
       </c>
     </row>
     <row r="339" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A339" s="1" t="s">
+        <v>722</v>
+      </c>
+      <c r="B339" s="1" t="s">
         <v>723</v>
       </c>
-      <c r="B339" s="1" t="s">
+      <c r="C339" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D339" s="1" t="s">
         <v>724</v>
       </c>
-      <c r="C339" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D339" s="1" t="s">
-        <v>722</v>
-      </c>
       <c r="E339" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F339" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="340" spans="1:6" x14ac:dyDescent="0.25">
@@ -9460,13 +9466,13 @@
         <v>3</v>
       </c>
       <c r="D340" s="1" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="E340" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F340" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="341" spans="1:6" x14ac:dyDescent="0.25">
@@ -9480,13 +9486,13 @@
         <v>3</v>
       </c>
       <c r="D341" s="1" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="E341" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F341" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="342" spans="1:6" x14ac:dyDescent="0.25">
@@ -9500,13 +9506,13 @@
         <v>3</v>
       </c>
       <c r="D342" s="1" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="E342" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F342" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="343" spans="1:6" x14ac:dyDescent="0.25">
@@ -9520,33 +9526,33 @@
         <v>3</v>
       </c>
       <c r="D343" s="1" t="s">
-        <v>733</v>
+        <v>724</v>
       </c>
       <c r="E343" s="1" t="s">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="F343" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="344" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A344" s="1" t="s">
+        <v>733</v>
+      </c>
+      <c r="B344" s="1" t="s">
         <v>734</v>
       </c>
-      <c r="B344" s="1" t="s">
+      <c r="C344" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D344" s="1" t="s">
         <v>735</v>
       </c>
-      <c r="C344" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D344" s="1" t="s">
-        <v>733</v>
-      </c>
       <c r="E344" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F344" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="345" spans="1:6" x14ac:dyDescent="0.25">
@@ -9560,13 +9566,13 @@
         <v>3</v>
       </c>
       <c r="D345" s="1" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="E345" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F345" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="346" spans="1:6" x14ac:dyDescent="0.25">
@@ -9580,13 +9586,13 @@
         <v>3</v>
       </c>
       <c r="D346" s="1" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="E346" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F346" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="347" spans="1:6" x14ac:dyDescent="0.25">
@@ -9600,13 +9606,13 @@
         <v>3</v>
       </c>
       <c r="D347" s="1" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="E347" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F347" s="1" t="s">
-        <v>12</v>
+        <v>85</v>
       </c>
     </row>
     <row r="348" spans="1:6" x14ac:dyDescent="0.25">
@@ -9620,33 +9626,33 @@
         <v>3</v>
       </c>
       <c r="D348" s="1" t="s">
-        <v>744</v>
+        <v>735</v>
       </c>
       <c r="E348" s="1" t="s">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="F348" s="1" t="s">
-        <v>745</v>
+        <v>12</v>
       </c>
     </row>
     <row r="349" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A349" s="1" t="s">
+        <v>744</v>
+      </c>
+      <c r="B349" s="1" t="s">
+        <v>745</v>
+      </c>
+      <c r="C349" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D349" s="1" t="s">
         <v>746</v>
       </c>
-      <c r="B349" s="1" t="s">
+      <c r="E349" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F349" s="1" t="s">
         <v>747</v>
-      </c>
-      <c r="C349" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D349" s="1" t="s">
-        <v>744</v>
-      </c>
-      <c r="E349" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F349" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="350" spans="1:6" x14ac:dyDescent="0.25">
@@ -9660,13 +9666,13 @@
         <v>3</v>
       </c>
       <c r="D350" s="1" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="E350" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F350" s="1" t="s">
-        <v>83</v>
+        <v>12</v>
       </c>
     </row>
     <row r="351" spans="1:6" x14ac:dyDescent="0.25">
@@ -9680,13 +9686,33 @@
         <v>3</v>
       </c>
       <c r="D351" s="1" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="E351" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F351" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="352" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A352" s="1" t="s">
+        <v>752</v>
+      </c>
+      <c r="B352" s="1" t="s">
+        <v>753</v>
+      </c>
+      <c r="C352" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D352" s="1" t="s">
+        <v>746</v>
+      </c>
+      <c r="E352" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F351" s="1" t="s">
-        <v>83</v>
+      <c r="F352" s="1" t="s">
+        <v>85</v>
       </c>
     </row>
   </sheetData>
